--- a/research/traditional_assets/database/data/switzerland/switzerland_retail_grocery_and_food.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_retail_grocery_and_food.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.06924579469179407</v>
+        <v>0.06918312583154404</v>
       </c>
       <c r="C2">
-        <v>111.5086463211265</v>
+        <v>110.4436239683614</v>
       </c>
       <c r="D2">
-        <v>91.00864632112652</v>
+        <v>91.08328925100852</v>
       </c>
       <c r="E2">
-        <v>-45.96652826471508</v>
+        <v>-44.82686298206793</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.139665282647151</v>
       </c>
       <c r="G2">
         <v>20.5</v>
@@ -1451,28 +1451,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.05732516371715168</v>
       </c>
       <c r="N2">
-        <v>7.390816326530611</v>
+        <v>7.33349116281346</v>
       </c>
       <c r="O2">
-        <v>1.079059183673469</v>
+        <v>1.070689709770765</v>
       </c>
       <c r="P2">
-        <v>6.311757142857142</v>
+        <v>6.262801453042695</v>
       </c>
       <c r="Q2">
-        <v>8.961757142857142</v>
+        <v>8.912801453042695</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.06924579469179407</v>
+        <v>0.06944804427428691</v>
       </c>
       <c r="T2">
-        <v>0.5414733185171841</v>
+        <v>0.5461442095678272</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>128.927958461622</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.06918312583154404</v>
+        <v>0.06912045697129403</v>
       </c>
       <c r="C3">
-        <v>110.4436239683614</v>
+        <v>109.378724156489</v>
       </c>
       <c r="D3">
-        <v>91.08328925100852</v>
+        <v>91.15805472178333</v>
       </c>
       <c r="E3">
-        <v>-44.82686298206793</v>
+        <v>-43.68719769942078</v>
       </c>
       <c r="F3">
-        <v>1.139665282647151</v>
+        <v>2.279330565294301</v>
       </c>
       <c r="G3">
         <v>20.5</v>
@@ -1533,28 +1533,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M3">
-        <v>0.05732516371715168</v>
+        <v>0.1146503274343034</v>
       </c>
       <c r="N3">
-        <v>7.33349116281346</v>
+        <v>7.276165999096309</v>
       </c>
       <c r="O3">
-        <v>1.070689709770765</v>
+        <v>1.062320235868061</v>
       </c>
       <c r="P3">
-        <v>6.262801453042695</v>
+        <v>6.213845763228248</v>
       </c>
       <c r="Q3">
-        <v>8.912801453042695</v>
+        <v>8.863845763228248</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.06944804427428691</v>
+        <v>0.06965442139927962</v>
       </c>
       <c r="T3">
-        <v>0.5461442095678272</v>
+        <v>0.5509104249256264</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>128.927958461622</v>
+        <v>64.46397923081099</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06912045697129403</v>
+        <v>0.069057788111044</v>
       </c>
       <c r="C4">
-        <v>109.378724156489</v>
+        <v>108.3139471875195</v>
       </c>
       <c r="D4">
-        <v>91.15805472178333</v>
+        <v>91.23294303546095</v>
       </c>
       <c r="E4">
-        <v>-43.68719769942078</v>
+        <v>-42.54753241677363</v>
       </c>
       <c r="F4">
-        <v>2.279330565294301</v>
+        <v>3.418995847941452</v>
       </c>
       <c r="G4">
         <v>20.5</v>
@@ -1615,28 +1615,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M4">
-        <v>0.1146503274343034</v>
+        <v>0.1719754911514551</v>
       </c>
       <c r="N4">
-        <v>7.276165999096309</v>
+        <v>7.218840835379156</v>
       </c>
       <c r="O4">
-        <v>1.062320235868061</v>
+        <v>1.053950761965357</v>
       </c>
       <c r="P4">
-        <v>6.213845763228248</v>
+        <v>6.164890073413799</v>
       </c>
       <c r="Q4">
-        <v>8.863845763228248</v>
+        <v>8.8148900734138</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.06965442139927962</v>
+        <v>0.06986505372272578</v>
       </c>
       <c r="T4">
-        <v>0.5509104249256264</v>
+        <v>0.5557749127650297</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>64.46397923081099</v>
+        <v>42.97598615387399</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.069057788111044</v>
+        <v>0.06899511925079399</v>
       </c>
       <c r="C5">
-        <v>108.3139471875195</v>
+        <v>107.249293364456</v>
       </c>
       <c r="D5">
-        <v>91.23294303546095</v>
+        <v>91.30795449504457</v>
       </c>
       <c r="E5">
-        <v>-42.54753241677363</v>
+        <v>-41.40786713412648</v>
       </c>
       <c r="F5">
-        <v>3.418995847941452</v>
+        <v>4.558661130588603</v>
       </c>
       <c r="G5">
         <v>20.5</v>
@@ -1697,28 +1697,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M5">
-        <v>0.1719754911514551</v>
+        <v>0.2293006548686067</v>
       </c>
       <c r="N5">
-        <v>7.218840835379156</v>
+        <v>7.161515671662005</v>
       </c>
       <c r="O5">
-        <v>1.053950761965357</v>
+        <v>1.045581288062653</v>
       </c>
       <c r="P5">
-        <v>6.164890073413799</v>
+        <v>6.115934383599352</v>
       </c>
       <c r="Q5">
-        <v>8.8148900734138</v>
+        <v>8.765934383599353</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.06986505372272578</v>
+        <v>0.07008007421957707</v>
       </c>
       <c r="T5">
-        <v>0.5557749127650297</v>
+        <v>0.5607407441010872</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>42.97598615387399</v>
+        <v>32.2319896154055</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06899511925079399</v>
+        <v>0.06893245039054396</v>
       </c>
       <c r="C6">
-        <v>107.249293364456</v>
+        <v>106.184762991299</v>
       </c>
       <c r="D6">
-        <v>91.30795449504457</v>
+        <v>91.3830894045348</v>
       </c>
       <c r="E6">
-        <v>-41.40786713412648</v>
+        <v>-40.26820185147933</v>
       </c>
       <c r="F6">
-        <v>4.558661130588603</v>
+        <v>5.698326413235755</v>
       </c>
       <c r="G6">
         <v>20.5</v>
@@ -1779,28 +1779,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M6">
-        <v>0.2293006548686067</v>
+        <v>0.2866258185857585</v>
       </c>
       <c r="N6">
-        <v>7.161515671662005</v>
+        <v>7.104190507944853</v>
       </c>
       <c r="O6">
-        <v>1.045581288062653</v>
+        <v>1.037211814159948</v>
       </c>
       <c r="P6">
-        <v>6.115934383599352</v>
+        <v>6.066978693784905</v>
       </c>
       <c r="Q6">
-        <v>8.765934383599353</v>
+        <v>8.716978693784904</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07008007421957707</v>
+        <v>0.07029962146373049</v>
       </c>
       <c r="T6">
-        <v>0.5607407441010872</v>
+        <v>0.5658111192547459</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>32.2319896154055</v>
+        <v>25.78559169232439</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06893245039054396</v>
+        <v>0.06886978153029394</v>
       </c>
       <c r="C7">
-        <v>106.184762991299</v>
+        <v>105.1203563730507</v>
       </c>
       <c r="D7">
-        <v>91.3830894045348</v>
+        <v>91.45834806893362</v>
       </c>
       <c r="E7">
-        <v>-40.26820185147933</v>
+        <v>-39.12853656883217</v>
       </c>
       <c r="F7">
-        <v>5.698326413235755</v>
+        <v>6.837991695882906</v>
       </c>
       <c r="G7">
         <v>20.5</v>
@@ -1861,28 +1861,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M7">
-        <v>0.2866258185857585</v>
+        <v>0.3439509823029102</v>
       </c>
       <c r="N7">
-        <v>7.104190507944853</v>
+        <v>7.046865344227701</v>
       </c>
       <c r="O7">
-        <v>1.037211814159948</v>
+        <v>1.028842340257244</v>
       </c>
       <c r="P7">
-        <v>6.066978693784905</v>
+        <v>6.018023003970457</v>
       </c>
       <c r="Q7">
-        <v>8.716978693784904</v>
+        <v>8.668023003970458</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07029962146373049</v>
+        <v>0.07052383992584463</v>
       </c>
       <c r="T7">
-        <v>0.5658111192547459</v>
+        <v>0.5709893747308229</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>25.78559169232439</v>
+        <v>21.48799307693699</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06886978153029394</v>
+        <v>0.06880711267004394</v>
       </c>
       <c r="C8">
-        <v>105.1203563730507</v>
+        <v>104.0560738157185</v>
       </c>
       <c r="D8">
-        <v>91.45834806893362</v>
+        <v>91.53373079424856</v>
       </c>
       <c r="E8">
-        <v>-39.12853656883217</v>
+        <v>-37.98887128618502</v>
       </c>
       <c r="F8">
-        <v>6.837991695882905</v>
+        <v>7.977656978530055</v>
       </c>
       <c r="G8">
         <v>20.5</v>
@@ -1943,28 +1943,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M8">
-        <v>0.3439509823029101</v>
+        <v>0.4012761460200617</v>
       </c>
       <c r="N8">
-        <v>7.046865344227701</v>
+        <v>6.989540180510549</v>
       </c>
       <c r="O8">
-        <v>1.028842340257244</v>
+        <v>1.02047286635454</v>
       </c>
       <c r="P8">
-        <v>6.018023003970457</v>
+        <v>5.96906731415601</v>
       </c>
       <c r="Q8">
-        <v>8.668023003970458</v>
+        <v>8.619067314156009</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07052383992584463</v>
+        <v>0.07075288029036982</v>
       </c>
       <c r="T8">
-        <v>0.5709893747308229</v>
+        <v>0.5762789905397188</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>21.48799307693699</v>
+        <v>18.41827978023171</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06880711267004393</v>
+        <v>0.0687444438097939</v>
       </c>
       <c r="C9">
-        <v>104.0560738157185</v>
+        <v>102.9919156263198</v>
       </c>
       <c r="D9">
-        <v>91.53373079424858</v>
+        <v>91.60923788749699</v>
       </c>
       <c r="E9">
-        <v>-37.98887128618502</v>
+        <v>-36.84920600353787</v>
       </c>
       <c r="F9">
-        <v>7.977656978530057</v>
+        <v>9.117322261177206</v>
       </c>
       <c r="G9">
         <v>20.5</v>
@@ -2025,28 +2025,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M9">
-        <v>0.4012761460200618</v>
+        <v>0.4586013097372134</v>
       </c>
       <c r="N9">
-        <v>6.989540180510549</v>
+        <v>6.932215016793398</v>
       </c>
       <c r="O9">
-        <v>1.02047286635454</v>
+        <v>1.012103392451836</v>
       </c>
       <c r="P9">
-        <v>5.96906731415601</v>
+        <v>5.920111624341562</v>
       </c>
       <c r="Q9">
-        <v>8.619067314156009</v>
+        <v>8.570111624341562</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07075288029036982</v>
+        <v>0.07098689979325425</v>
       </c>
       <c r="T9">
-        <v>0.5762789905397188</v>
+        <v>0.581683597996634</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>18.41827978023171</v>
+        <v>16.11599480770275</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0687444438097939</v>
+        <v>0.06868177494954389</v>
       </c>
       <c r="C10">
-        <v>102.9919156263198</v>
+        <v>101.9278821128857</v>
       </c>
       <c r="D10">
-        <v>91.60923788749699</v>
+        <v>91.68486965671001</v>
       </c>
       <c r="E10">
-        <v>-36.84920600353787</v>
+        <v>-35.70954072089072</v>
       </c>
       <c r="F10">
-        <v>9.117322261177206</v>
+        <v>10.25698754382436</v>
       </c>
       <c r="G10">
         <v>20.5</v>
@@ -2107,28 +2107,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M10">
-        <v>0.4586013097372134</v>
+        <v>0.5159264734543652</v>
       </c>
       <c r="N10">
-        <v>6.932215016793398</v>
+        <v>6.874889853076247</v>
       </c>
       <c r="O10">
-        <v>1.012103392451836</v>
+        <v>1.003733918549132</v>
       </c>
       <c r="P10">
-        <v>5.920111624341562</v>
+        <v>5.871155934527115</v>
       </c>
       <c r="Q10">
-        <v>8.570111624341562</v>
+        <v>8.521155934527116</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07098689979325425</v>
+        <v>0.07122606258191636</v>
       </c>
       <c r="T10">
-        <v>0.581683597996634</v>
+        <v>0.58720698803502</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.11599480770275</v>
+        <v>14.325328717958</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06868177494954389</v>
+        <v>0.06861910608929388</v>
       </c>
       <c r="C11">
-        <v>101.9278821128857</v>
+        <v>100.8639735844654</v>
       </c>
       <c r="D11">
-        <v>91.68486965671001</v>
+        <v>91.76062641093688</v>
       </c>
       <c r="E11">
-        <v>-35.70954072089072</v>
+        <v>-34.56987543824357</v>
       </c>
       <c r="F11">
-        <v>10.25698754382436</v>
+        <v>11.39665282647151</v>
       </c>
       <c r="G11">
         <v>20.5</v>
@@ -2189,28 +2189,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M11">
-        <v>0.5159264734543652</v>
+        <v>0.5732516371715168</v>
       </c>
       <c r="N11">
-        <v>6.874889853076247</v>
+        <v>6.817564689359095</v>
       </c>
       <c r="O11">
-        <v>1.003733918549132</v>
+        <v>0.9953644446464278</v>
       </c>
       <c r="P11">
-        <v>5.871155934527115</v>
+        <v>5.822200244712668</v>
       </c>
       <c r="Q11">
-        <v>8.521155934527116</v>
+        <v>8.472200244712667</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07122606258191636</v>
+        <v>0.07147054009921541</v>
       </c>
       <c r="T11">
-        <v>0.58720698803502</v>
+        <v>0.5928531200742591</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>14.325328717958</v>
+        <v>12.8927958461622</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06861910608929388</v>
+        <v>0.06869734722904386</v>
       </c>
       <c r="C12">
-        <v>100.8639735844654</v>
+        <v>99.6297465202111</v>
       </c>
       <c r="D12">
-        <v>91.76062641093688</v>
+        <v>91.66606462932975</v>
       </c>
       <c r="E12">
-        <v>-34.56987543824357</v>
+        <v>-33.43021015559642</v>
       </c>
       <c r="F12">
-        <v>11.39665282647151</v>
+        <v>12.53631810911866</v>
       </c>
       <c r="G12">
         <v>20.5</v>
@@ -2271,45 +2271,45 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M12">
-        <v>0.5732516371715169</v>
+        <v>0.6493812780523465</v>
       </c>
       <c r="N12">
-        <v>6.817564689359094</v>
+        <v>6.741435048478265</v>
       </c>
       <c r="O12">
-        <v>0.9953644446464277</v>
+        <v>0.9842495170778266</v>
       </c>
       <c r="P12">
-        <v>5.822200244712667</v>
+        <v>5.757185531400438</v>
       </c>
       <c r="Q12">
-        <v>8.472200244712667</v>
+        <v>8.407185531400438</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07147054009921541</v>
+        <v>0.0717205114933077</v>
       </c>
       <c r="T12">
-        <v>0.5928531200742591</v>
+        <v>0.5986261314851664</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.146</v>
       </c>
       <c r="W12">
-        <v>0.0429562</v>
+        <v>0.0442372</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>12.89279584616219</v>
+        <v>11.38132030645768</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06869734722904386</v>
+        <v>0.06864748836879382</v>
       </c>
       <c r="C13">
-        <v>99.6297465202111</v>
+        <v>98.55031782166799</v>
       </c>
       <c r="D13">
-        <v>91.66606462932975</v>
+        <v>91.7263012134338</v>
       </c>
       <c r="E13">
-        <v>-33.43021015559642</v>
+        <v>-32.29054487294927</v>
       </c>
       <c r="F13">
-        <v>12.53631810911866</v>
+        <v>13.67598339176581</v>
       </c>
       <c r="G13">
         <v>20.5</v>
@@ -2353,28 +2353,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M13">
-        <v>0.6493812780523465</v>
+        <v>0.7084159396934689</v>
       </c>
       <c r="N13">
-        <v>6.741435048478265</v>
+        <v>6.682400386837142</v>
       </c>
       <c r="O13">
-        <v>0.9842495170778266</v>
+        <v>0.9756304564782227</v>
       </c>
       <c r="P13">
-        <v>5.757185531400438</v>
+        <v>5.706769930358919</v>
       </c>
       <c r="Q13">
-        <v>8.407185531400438</v>
+        <v>8.356769930358919</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0717205114933077</v>
+        <v>0.07197616405544753</v>
       </c>
       <c r="T13">
-        <v>0.5986261314851664</v>
+        <v>0.604530347700867</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.38132030645768</v>
+        <v>10.43287694758621</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06864748836879382</v>
+        <v>0.06878636350854381</v>
       </c>
       <c r="C14">
-        <v>98.55031782166799</v>
+        <v>97.24306813123248</v>
       </c>
       <c r="D14">
-        <v>91.7263012134338</v>
+        <v>91.55871680564543</v>
       </c>
       <c r="E14">
-        <v>-32.29054487294927</v>
+        <v>-31.15087959030212</v>
       </c>
       <c r="F14">
-        <v>13.67598339176581</v>
+        <v>14.81564867441296</v>
       </c>
       <c r="G14">
         <v>20.5</v>
@@ -2435,45 +2435,45 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M14">
-        <v>0.7084159396934689</v>
+        <v>0.7926372040810934</v>
       </c>
       <c r="N14">
-        <v>6.682400386837142</v>
+        <v>6.598179122449518</v>
       </c>
       <c r="O14">
-        <v>0.9756304564782227</v>
+        <v>0.9633341518776296</v>
       </c>
       <c r="P14">
-        <v>5.706769930358919</v>
+        <v>5.634844970571889</v>
       </c>
       <c r="Q14">
-        <v>8.356769930358919</v>
+        <v>8.284844970571889</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07197616405544753</v>
+        <v>0.07223769368798139</v>
       </c>
       <c r="T14">
-        <v>0.604530347700867</v>
+        <v>0.6105702930249746</v>
       </c>
       <c r="U14">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V14">
         <v>0.146</v>
       </c>
       <c r="W14">
-        <v>0.0442372</v>
+        <v>0.045689</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>10.43287694758621</v>
+        <v>9.324336895211481</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06878636350854381</v>
+        <v>0.06875102264829379</v>
       </c>
       <c r="C15">
-        <v>97.24306813123248</v>
+        <v>96.1459915108195</v>
       </c>
       <c r="D15">
-        <v>91.55871680564543</v>
+        <v>91.60130546787961</v>
       </c>
       <c r="E15">
-        <v>-31.15087959030212</v>
+        <v>-30.01121430765497</v>
       </c>
       <c r="F15">
-        <v>14.81564867441296</v>
+        <v>15.95531395706011</v>
       </c>
       <c r="G15">
         <v>20.5</v>
@@ -2517,28 +2517,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M15">
-        <v>0.7926372040810934</v>
+        <v>0.853609296702716</v>
       </c>
       <c r="N15">
-        <v>6.598179122449518</v>
+        <v>6.537207029827895</v>
       </c>
       <c r="O15">
-        <v>0.9633341518776296</v>
+        <v>0.9544322263548727</v>
       </c>
       <c r="P15">
-        <v>5.634844970571889</v>
+        <v>5.582774803473023</v>
       </c>
       <c r="Q15">
-        <v>8.284844970571889</v>
+        <v>8.232774803473022</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07223769368798139</v>
+        <v>0.07250530540499278</v>
       </c>
       <c r="T15">
-        <v>0.6105702930249746</v>
+        <v>0.6167507021938289</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>9.324336895211481</v>
+        <v>8.658312831267803</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06875102264829379</v>
+        <v>0.06871568178804377</v>
       </c>
       <c r="C16">
-        <v>96.1459915108195</v>
+        <v>95.04895452919342</v>
       </c>
       <c r="D16">
-        <v>91.60130546787961</v>
+        <v>91.64393376890069</v>
       </c>
       <c r="E16">
-        <v>-30.01121430765497</v>
+        <v>-28.87154902500782</v>
       </c>
       <c r="F16">
-        <v>15.95531395706011</v>
+        <v>17.09497923970726</v>
       </c>
       <c r="G16">
         <v>20.5</v>
@@ -2599,28 +2599,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M16">
-        <v>0.853609296702716</v>
+        <v>0.9145813893243386</v>
       </c>
       <c r="N16">
-        <v>6.537207029827895</v>
+        <v>6.476234937206273</v>
       </c>
       <c r="O16">
-        <v>0.9544322263548727</v>
+        <v>0.9455303008321159</v>
       </c>
       <c r="P16">
-        <v>5.582774803473023</v>
+        <v>5.530704636374157</v>
       </c>
       <c r="Q16">
-        <v>8.232774803473022</v>
+        <v>8.180704636374157</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07250530540499278</v>
+        <v>0.07277921386828679</v>
       </c>
       <c r="T16">
-        <v>0.6167507021938289</v>
+        <v>0.6230765327548915</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.658312831267803</v>
+        <v>8.081091975849951</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06871568178804377</v>
+        <v>0.06878965292779375</v>
       </c>
       <c r="C17">
-        <v>95.04895452919344</v>
+        <v>93.82011027525394</v>
       </c>
       <c r="D17">
-        <v>91.64393376890069</v>
+        <v>91.55475479760835</v>
       </c>
       <c r="E17">
-        <v>-28.87154902500782</v>
+        <v>-27.73188374236067</v>
       </c>
       <c r="F17">
-        <v>17.09497923970726</v>
+        <v>18.23464452235441</v>
       </c>
       <c r="G17">
         <v>20.5</v>
@@ -2681,45 +2681,45 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M17">
-        <v>0.9145813893243384</v>
+        <v>0.9901411975638446</v>
       </c>
       <c r="N17">
-        <v>6.476234937206273</v>
+        <v>6.400675128966767</v>
       </c>
       <c r="O17">
-        <v>0.9455303008321159</v>
+        <v>0.9344985688291478</v>
       </c>
       <c r="P17">
-        <v>5.530704636374157</v>
+        <v>5.466176560137619</v>
       </c>
       <c r="Q17">
-        <v>8.180704636374157</v>
+        <v>8.116176560137619</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07277921386828679</v>
+        <v>0.07305964396165923</v>
       </c>
       <c r="T17">
-        <v>0.6230765327548915</v>
+        <v>0.6295529783293127</v>
       </c>
       <c r="U17">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V17">
         <v>0.146</v>
       </c>
       <c r="W17">
-        <v>0.045689</v>
+        <v>0.0463722</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y17">
-        <v>8.081091975849951</v>
+        <v>7.464406434875213</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06878965292779375</v>
+        <v>0.06876114406754373</v>
       </c>
       <c r="C18">
-        <v>93.82011027525394</v>
+        <v>92.71479446668013</v>
       </c>
       <c r="D18">
-        <v>91.55475479760835</v>
+        <v>91.58910427168171</v>
       </c>
       <c r="E18">
-        <v>-27.73188374236067</v>
+        <v>-26.59221845971351</v>
       </c>
       <c r="F18">
-        <v>18.23464452235441</v>
+        <v>19.37430980500157</v>
       </c>
       <c r="G18">
         <v>20.5</v>
@@ -2763,28 +2763,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M18">
-        <v>0.9901411975638446</v>
+        <v>1.052025022411585</v>
       </c>
       <c r="N18">
-        <v>6.400675128966767</v>
+        <v>6.338791304119026</v>
       </c>
       <c r="O18">
-        <v>0.9344985688291478</v>
+        <v>0.9254635304013779</v>
       </c>
       <c r="P18">
-        <v>5.466176560137619</v>
+        <v>5.413327773717649</v>
       </c>
       <c r="Q18">
-        <v>8.116176560137619</v>
+        <v>8.063327773717649</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07305964396165923</v>
+        <v>0.07334683140667919</v>
       </c>
       <c r="T18">
-        <v>0.6295529783293127</v>
+        <v>0.6361854828332379</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.464406434875213</v>
+        <v>7.025323703411964</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06876114406754373</v>
+        <v>0.06873263520729371</v>
       </c>
       <c r="C19">
-        <v>92.71479446668013</v>
+        <v>91.60950444222226</v>
       </c>
       <c r="D19">
-        <v>91.58910427168171</v>
+        <v>91.62347952987098</v>
       </c>
       <c r="E19">
-        <v>-26.59221845971351</v>
+        <v>-25.45255317706636</v>
       </c>
       <c r="F19">
-        <v>19.37430980500157</v>
+        <v>20.51397508764872</v>
       </c>
       <c r="G19">
         <v>20.5</v>
@@ -2845,28 +2845,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M19">
-        <v>1.052025022411585</v>
+        <v>1.113908847259325</v>
       </c>
       <c r="N19">
-        <v>6.338791304119026</v>
+        <v>6.276907479271286</v>
       </c>
       <c r="O19">
-        <v>0.9254635304013779</v>
+        <v>0.9164284919736078</v>
       </c>
       <c r="P19">
-        <v>5.413327773717649</v>
+        <v>5.360478987297679</v>
       </c>
       <c r="Q19">
-        <v>8.063327773717649</v>
+        <v>8.010478987297679</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07334683140667919</v>
+        <v>0.07364102342352892</v>
       </c>
       <c r="T19">
-        <v>0.6361854828332379</v>
+        <v>0.6429797557396981</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.025323703411964</v>
+        <v>6.6350279421113</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06873263520729372</v>
+        <v>0.06870412634704369</v>
       </c>
       <c r="C20">
-        <v>91.60950444222223</v>
+        <v>90.50424023092309</v>
       </c>
       <c r="D20">
-        <v>91.62347952987095</v>
+        <v>91.65788060121895</v>
       </c>
       <c r="E20">
-        <v>-25.45255317706637</v>
+        <v>-24.31288789441922</v>
       </c>
       <c r="F20">
-        <v>20.51397508764871</v>
+        <v>21.65364037029586</v>
       </c>
       <c r="G20">
         <v>20.5</v>
@@ -2927,28 +2927,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M20">
-        <v>1.113908847259325</v>
+        <v>1.175792672107066</v>
       </c>
       <c r="N20">
-        <v>6.276907479271286</v>
+        <v>6.215023654423546</v>
       </c>
       <c r="O20">
-        <v>0.9164284919736078</v>
+        <v>0.9073934535458377</v>
       </c>
       <c r="P20">
-        <v>5.360478987297679</v>
+        <v>5.307630200877709</v>
       </c>
       <c r="Q20">
-        <v>8.010478987297679</v>
+        <v>7.957630200877709</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07364102342352892</v>
+        <v>0.07394247944079468</v>
       </c>
       <c r="T20">
-        <v>0.6429797557396981</v>
+        <v>0.6499417884710091</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.6350279421113</v>
+        <v>6.285815945158074</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06870412634704369</v>
+        <v>0.06884641748679368</v>
       </c>
       <c r="C21">
-        <v>90.50424023092309</v>
+        <v>89.19313188935611</v>
       </c>
       <c r="D21">
-        <v>91.65788060121895</v>
+        <v>91.48643754229913</v>
       </c>
       <c r="E21">
-        <v>-24.31288789441922</v>
+        <v>-23.17322261177206</v>
       </c>
       <c r="F21">
-        <v>21.65364037029586</v>
+        <v>22.79330565294302</v>
       </c>
       <c r="G21">
         <v>20.5</v>
@@ -3009,45 +3009,45 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M21">
-        <v>1.175792672107066</v>
+        <v>1.260469802607749</v>
       </c>
       <c r="N21">
-        <v>6.215023654423546</v>
+        <v>6.130346523922863</v>
       </c>
       <c r="O21">
-        <v>0.9073934535458377</v>
+        <v>0.8950305924927379</v>
       </c>
       <c r="P21">
-        <v>5.307630200877709</v>
+        <v>5.235315931430125</v>
       </c>
       <c r="Q21">
-        <v>7.957630200877709</v>
+        <v>7.885315931430124</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07394247944079468</v>
+        <v>0.0742514718584921</v>
       </c>
       <c r="T21">
-        <v>0.6499417884710091</v>
+        <v>0.6570778720206029</v>
       </c>
       <c r="U21">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V21">
         <v>0.146</v>
       </c>
       <c r="W21">
-        <v>0.0463722</v>
+        <v>0.0472262</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y21">
-        <v>6.285815945158074</v>
+        <v>5.863540968010474</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06884641748679368</v>
+        <v>0.06882644862654366</v>
       </c>
       <c r="C22">
-        <v>89.19313188935611</v>
+        <v>88.07748789240043</v>
       </c>
       <c r="D22">
-        <v>91.48643754229913</v>
+        <v>91.5104588279906</v>
       </c>
       <c r="E22">
-        <v>-23.17322261177206</v>
+        <v>-22.03355732912491</v>
       </c>
       <c r="F22">
-        <v>22.79330565294302</v>
+        <v>23.93297093559017</v>
       </c>
       <c r="G22">
         <v>20.5</v>
@@ -3091,28 +3091,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M22">
-        <v>1.260469802607749</v>
+        <v>1.323493292738136</v>
       </c>
       <c r="N22">
-        <v>6.130346523922863</v>
+        <v>6.067323033792475</v>
       </c>
       <c r="O22">
-        <v>0.8950305924927379</v>
+        <v>0.8858291629337013</v>
       </c>
       <c r="P22">
-        <v>5.235315931430125</v>
+        <v>5.181493870858773</v>
       </c>
       <c r="Q22">
-        <v>7.885315931430124</v>
+        <v>7.831493870858774</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0742514718584921</v>
+        <v>0.0745682868690426</v>
       </c>
       <c r="T22">
-        <v>0.6570778720206029</v>
+        <v>0.6643946159132242</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.863540968010474</v>
+        <v>5.584324731438547</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06882644862654365</v>
+        <v>0.06880647976629364</v>
       </c>
       <c r="C23">
-        <v>88.07748789240046</v>
+        <v>86.96185651313387</v>
       </c>
       <c r="D23">
-        <v>91.51045882799062</v>
+        <v>91.53449273137119</v>
       </c>
       <c r="E23">
-        <v>-22.03355732912491</v>
+        <v>-20.89389204647776</v>
       </c>
       <c r="F23">
-        <v>23.93297093559017</v>
+        <v>25.07263621823732</v>
       </c>
       <c r="G23">
         <v>20.5</v>
@@ -3173,28 +3173,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M23">
-        <v>1.323493292738136</v>
+        <v>1.386516782868524</v>
       </c>
       <c r="N23">
-        <v>6.067323033792476</v>
+        <v>6.004299543662087</v>
       </c>
       <c r="O23">
-        <v>0.8858291629337014</v>
+        <v>0.8766277333746647</v>
       </c>
       <c r="P23">
-        <v>5.181493870858774</v>
+        <v>5.127671810287422</v>
       </c>
       <c r="Q23">
-        <v>7.831493870858774</v>
+        <v>7.777671810287423</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0745682868690426</v>
+        <v>0.07489322534140211</v>
       </c>
       <c r="T23">
-        <v>0.6643946159132242</v>
+        <v>0.6718989686236053</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.584324731438548</v>
+        <v>5.330491789100432</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06880647976629364</v>
+        <v>0.06878651090604362</v>
       </c>
       <c r="C24">
-        <v>86.96185651313387</v>
+        <v>85.84623776150057</v>
       </c>
       <c r="D24">
-        <v>91.53449273137119</v>
+        <v>91.55853926238504</v>
       </c>
       <c r="E24">
-        <v>-20.89389204647776</v>
+        <v>-19.75422676383061</v>
       </c>
       <c r="F24">
-        <v>25.07263621823732</v>
+        <v>26.21230150088447</v>
       </c>
       <c r="G24">
         <v>20.5</v>
@@ -3255,28 +3255,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M24">
-        <v>1.386516782868524</v>
+        <v>1.449540272998911</v>
       </c>
       <c r="N24">
-        <v>6.004299543662087</v>
+        <v>5.9412760535317</v>
       </c>
       <c r="O24">
-        <v>0.8766277333746647</v>
+        <v>0.8674263038156281</v>
       </c>
       <c r="P24">
-        <v>5.127671810287422</v>
+        <v>5.073849749716072</v>
       </c>
       <c r="Q24">
-        <v>7.777671810287423</v>
+        <v>7.723849749716072</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07489322534140211</v>
+        <v>0.07522660377408262</v>
       </c>
       <c r="T24">
-        <v>0.6718989686236053</v>
+        <v>0.6795982395862039</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.330491789100432</v>
+        <v>5.098731276530848</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06878651090604362</v>
+        <v>0.0687665420457936</v>
       </c>
       <c r="C25">
-        <v>85.84623776150057</v>
+        <v>84.73063164745516</v>
       </c>
       <c r="D25">
-        <v>91.55853926238504</v>
+        <v>91.58259843098678</v>
       </c>
       <c r="E25">
-        <v>-19.75422676383061</v>
+        <v>-18.61456148118346</v>
       </c>
       <c r="F25">
-        <v>26.21230150088447</v>
+        <v>27.35196678353162</v>
       </c>
       <c r="G25">
         <v>20.5</v>
@@ -3337,28 +3337,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M25">
-        <v>1.449540272998911</v>
+        <v>1.512563763129299</v>
       </c>
       <c r="N25">
-        <v>5.9412760535317</v>
+        <v>5.878252563401313</v>
       </c>
       <c r="O25">
-        <v>0.8674263038156281</v>
+        <v>0.8582248742565917</v>
       </c>
       <c r="P25">
-        <v>5.073849749716072</v>
+        <v>5.020027689144722</v>
       </c>
       <c r="Q25">
-        <v>7.723849749716072</v>
+        <v>7.670027689144721</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07522660377408262</v>
+        <v>0.07556875532341263</v>
       </c>
       <c r="T25">
-        <v>0.6795982395862039</v>
+        <v>0.6875001229425551</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.098731276530848</v>
+        <v>4.886284140008728</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0687665420457936</v>
+        <v>0.06874657318554359</v>
       </c>
       <c r="C26">
-        <v>84.73063164745516</v>
+        <v>83.61503818096276</v>
       </c>
       <c r="D26">
-        <v>91.58259843098678</v>
+        <v>91.60667024714152</v>
       </c>
       <c r="E26">
-        <v>-18.61456148118346</v>
+        <v>-17.47489619853631</v>
       </c>
       <c r="F26">
-        <v>27.35196678353162</v>
+        <v>28.49163206617877</v>
       </c>
       <c r="G26">
         <v>20.5</v>
@@ -3419,28 +3419,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M26">
-        <v>1.512563763129299</v>
+        <v>1.575587253259686</v>
       </c>
       <c r="N26">
-        <v>5.878252563401313</v>
+        <v>5.815229073270926</v>
       </c>
       <c r="O26">
-        <v>0.8582248742565917</v>
+        <v>0.8490234446975551</v>
       </c>
       <c r="P26">
-        <v>5.020027689144722</v>
+        <v>4.966205628573371</v>
       </c>
       <c r="Q26">
-        <v>7.670027689144721</v>
+        <v>7.61620562857337</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07556875532341263</v>
+        <v>0.07592003091405811</v>
       </c>
       <c r="T26">
-        <v>0.6875001229425551</v>
+        <v>0.6956127231884091</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.886284140008729</v>
+        <v>4.69083277440838</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06874657318554359</v>
+        <v>0.06872660432529357</v>
       </c>
       <c r="C27">
-        <v>83.61503818096276</v>
+        <v>82.49945737199891</v>
       </c>
       <c r="D27">
-        <v>91.60667024714152</v>
+        <v>91.63075472082484</v>
       </c>
       <c r="E27">
-        <v>-17.47489619853631</v>
+        <v>-16.33523091588916</v>
       </c>
       <c r="F27">
-        <v>28.49163206617877</v>
+        <v>29.63129734882592</v>
       </c>
       <c r="G27">
         <v>20.5</v>
@@ -3501,28 +3501,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M27">
-        <v>1.575587253259686</v>
+        <v>1.638610743390073</v>
       </c>
       <c r="N27">
-        <v>5.815229073270926</v>
+        <v>5.752205583140539</v>
       </c>
       <c r="O27">
-        <v>0.8490234446975551</v>
+        <v>0.8398220151385186</v>
       </c>
       <c r="P27">
-        <v>4.966205628573371</v>
+        <v>4.91238356800202</v>
       </c>
       <c r="Q27">
-        <v>7.61620562857337</v>
+        <v>7.562383568002019</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07592003091405811</v>
+        <v>0.07628080043958589</v>
       </c>
       <c r="T27">
-        <v>0.6956127231884091</v>
+        <v>0.7039445829003672</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.69083277440838</v>
+        <v>4.510416129238827</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06872660432529357</v>
+        <v>0.06928308546504354</v>
       </c>
       <c r="C28">
-        <v>82.49945737199891</v>
+        <v>80.69332583928527</v>
       </c>
       <c r="D28">
-        <v>91.63075472082484</v>
+        <v>90.96428847075833</v>
       </c>
       <c r="E28">
-        <v>-16.33523091588916</v>
+        <v>-15.19556563324201</v>
       </c>
       <c r="F28">
-        <v>29.63129734882592</v>
+        <v>30.77096263147307</v>
       </c>
       <c r="G28">
         <v>20.5</v>
@@ -3583,45 +3583,45 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M28">
-        <v>1.638610743390073</v>
+        <v>1.778561640099144</v>
       </c>
       <c r="N28">
-        <v>5.752205583140539</v>
+        <v>5.612254686431468</v>
       </c>
       <c r="O28">
-        <v>0.8398220151385186</v>
+        <v>0.8193891842189943</v>
       </c>
       <c r="P28">
-        <v>4.91238356800202</v>
+        <v>4.792865502212474</v>
       </c>
       <c r="Q28">
-        <v>7.562383568002019</v>
+        <v>7.442865502212474</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07628080043958589</v>
+        <v>0.07665145406170348</v>
       </c>
       <c r="T28">
-        <v>0.7039445829003672</v>
+        <v>0.7125047127414201</v>
       </c>
       <c r="U28">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V28">
         <v>0.146</v>
       </c>
       <c r="W28">
-        <v>0.0472262</v>
+        <v>0.0493612</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.510416129238827</v>
+        <v>4.155501929142371</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06928308546504354</v>
+        <v>0.06928446660479352</v>
       </c>
       <c r="C29">
-        <v>80.69332583928527</v>
+        <v>79.55201850367899</v>
       </c>
       <c r="D29">
-        <v>90.96428847075833</v>
+        <v>90.96264641779922</v>
       </c>
       <c r="E29">
-        <v>-15.19556563324201</v>
+        <v>-14.05590035059485</v>
       </c>
       <c r="F29">
-        <v>30.77096263147307</v>
+        <v>31.91062791412023</v>
       </c>
       <c r="G29">
         <v>20.5</v>
@@ -3665,28 +3665,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M29">
-        <v>1.778561640099144</v>
+        <v>1.844434293436149</v>
       </c>
       <c r="N29">
-        <v>5.612254686431468</v>
+        <v>5.546382033094462</v>
       </c>
       <c r="O29">
-        <v>0.8193891842189943</v>
+        <v>0.8097717768317914</v>
       </c>
       <c r="P29">
-        <v>4.792865502212474</v>
+        <v>4.73661025626267</v>
       </c>
       <c r="Q29">
-        <v>7.442865502212474</v>
+        <v>7.386610256262671</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07665145406170348</v>
+        <v>0.07703240361776878</v>
       </c>
       <c r="T29">
-        <v>0.7125047127414201</v>
+        <v>0.7213026239669467</v>
       </c>
       <c r="U29">
         <v>0.0578</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.155501929142371</v>
+        <v>4.007091145958714</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06928446660479352</v>
+        <v>0.07015265774454349</v>
       </c>
       <c r="C30">
-        <v>79.55201850367899</v>
+        <v>77.39175052939407</v>
       </c>
       <c r="D30">
-        <v>90.96264641779922</v>
+        <v>89.94204372616146</v>
       </c>
       <c r="E30">
-        <v>-14.05590035059485</v>
+        <v>-12.9162350679477</v>
       </c>
       <c r="F30">
-        <v>31.91062791412023</v>
+        <v>33.05029319676738</v>
       </c>
       <c r="G30">
         <v>20.5</v>
@@ -3747,45 +3747,45 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M30">
-        <v>1.844434293436149</v>
+        <v>2.02598297296184</v>
       </c>
       <c r="N30">
-        <v>5.546382033094462</v>
+        <v>5.364833353568772</v>
       </c>
       <c r="O30">
-        <v>0.8097717768317914</v>
+        <v>0.7832656696210406</v>
       </c>
       <c r="P30">
-        <v>4.73661025626267</v>
+        <v>4.581567683947731</v>
       </c>
       <c r="Q30">
-        <v>7.386610256262671</v>
+        <v>7.231567683947731</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07703240361776878</v>
+        <v>0.07742408414724436</v>
       </c>
       <c r="T30">
-        <v>0.7213026239669467</v>
+        <v>0.7303483636776993</v>
       </c>
       <c r="U30">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V30">
         <v>0.146</v>
       </c>
       <c r="W30">
-        <v>0.0493612</v>
+        <v>0.0523502</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.007091145958714</v>
+        <v>3.648015025380877</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07015265774454349</v>
+        <v>0.07018392888429348</v>
       </c>
       <c r="C31">
-        <v>77.39175052939409</v>
+        <v>76.21575157746906</v>
       </c>
       <c r="D31">
-        <v>89.94204372616146</v>
+        <v>89.90571005688359</v>
       </c>
       <c r="E31">
-        <v>-12.91623506794771</v>
+        <v>-11.77656978530056</v>
       </c>
       <c r="F31">
-        <v>33.05029319676737</v>
+        <v>34.18995847941452</v>
       </c>
       <c r="G31">
         <v>20.5</v>
@@ -3829,28 +3829,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M31">
-        <v>2.02598297296184</v>
+        <v>2.09584445478811</v>
       </c>
       <c r="N31">
-        <v>5.364833353568772</v>
+        <v>5.294971871742501</v>
       </c>
       <c r="O31">
-        <v>0.7832656696210406</v>
+        <v>0.773065893274405</v>
       </c>
       <c r="P31">
-        <v>4.581567683947731</v>
+        <v>4.521905978468096</v>
       </c>
       <c r="Q31">
-        <v>7.231567683947731</v>
+        <v>7.171905978468097</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07742408414724436</v>
+        <v>0.07782695554899069</v>
       </c>
       <c r="T31">
-        <v>0.7303483636776993</v>
+        <v>0.7396525530944734</v>
       </c>
       <c r="U31">
         <v>0.0613</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.648015025380877</v>
+        <v>3.526414524534847</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07018392888429348</v>
+        <v>0.07095647202404345</v>
       </c>
       <c r="C32">
-        <v>76.21575157746906</v>
+        <v>74.18770360446861</v>
       </c>
       <c r="D32">
-        <v>89.90571005688359</v>
+        <v>89.01732736653028</v>
       </c>
       <c r="E32">
-        <v>-11.77656978530056</v>
+        <v>-10.63690450265341</v>
       </c>
       <c r="F32">
-        <v>34.18995847941452</v>
+        <v>35.32962376206167</v>
       </c>
       <c r="G32">
         <v>20.5</v>
@@ -3911,45 +3911,45 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M32">
-        <v>2.09584445478811</v>
+        <v>2.264628883148153</v>
       </c>
       <c r="N32">
-        <v>5.294971871742501</v>
+        <v>5.126187443382458</v>
       </c>
       <c r="O32">
-        <v>0.773065893274405</v>
+        <v>0.7484233667338388</v>
       </c>
       <c r="P32">
-        <v>4.521905978468096</v>
+        <v>4.377764076648619</v>
       </c>
       <c r="Q32">
-        <v>7.171905978468097</v>
+        <v>7.027764076648619</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07782695554899069</v>
+        <v>0.07824150438267169</v>
       </c>
       <c r="T32">
-        <v>0.7396525530944734</v>
+        <v>0.7492264291610092</v>
       </c>
       <c r="U32">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V32">
         <v>0.146</v>
       </c>
       <c r="W32">
-        <v>0.0523502</v>
+        <v>0.0547414</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>3.526414524534847</v>
+        <v>3.263588299843785</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07095647202404345</v>
+        <v>0.07101165516379344</v>
       </c>
       <c r="C33">
-        <v>74.18770360446861</v>
+        <v>72.98525206346221</v>
       </c>
       <c r="D33">
-        <v>89.01732736653028</v>
+        <v>88.95454110817104</v>
       </c>
       <c r="E33">
-        <v>-10.63690450265341</v>
+        <v>-9.497239220006257</v>
       </c>
       <c r="F33">
-        <v>35.32962376206167</v>
+        <v>36.46928904470882</v>
       </c>
       <c r="G33">
         <v>20.5</v>
@@ -3993,28 +3993,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M33">
-        <v>2.264628883148153</v>
+        <v>2.337681427765836</v>
       </c>
       <c r="N33">
-        <v>5.126187443382458</v>
+        <v>5.053134898764776</v>
       </c>
       <c r="O33">
-        <v>0.7484233667338388</v>
+        <v>0.7377576952196573</v>
       </c>
       <c r="P33">
-        <v>4.377764076648619</v>
+        <v>4.315377203545119</v>
       </c>
       <c r="Q33">
-        <v>7.027764076648619</v>
+        <v>6.965377203545119</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07824150438267169</v>
+        <v>0.078668245829108</v>
       </c>
       <c r="T33">
-        <v>0.7492264291610092</v>
+        <v>0.7590818898177372</v>
       </c>
       <c r="U33">
         <v>0.0641</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.263588299843785</v>
+        <v>3.161601165473667</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07101165516379344</v>
+        <v>0.07106683830354343</v>
       </c>
       <c r="C34">
-        <v>72.98525206346221</v>
+        <v>71.78288902962265</v>
       </c>
       <c r="D34">
-        <v>88.95454110817104</v>
+        <v>88.89184335697863</v>
       </c>
       <c r="E34">
-        <v>-9.497239220006257</v>
+        <v>-8.357573937359099</v>
       </c>
       <c r="F34">
-        <v>36.46928904470882</v>
+        <v>37.60895432735598</v>
       </c>
       <c r="G34">
         <v>20.5</v>
@@ -4075,28 +4075,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M34">
-        <v>2.337681427765836</v>
+        <v>2.410733972383519</v>
       </c>
       <c r="N34">
-        <v>5.053134898764776</v>
+        <v>4.980082354147093</v>
       </c>
       <c r="O34">
-        <v>0.7377576952196573</v>
+        <v>0.7270920237054755</v>
       </c>
       <c r="P34">
-        <v>4.315377203545119</v>
+        <v>4.252990330441618</v>
       </c>
       <c r="Q34">
-        <v>6.965377203545119</v>
+        <v>6.902990330441618</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.078668245829108</v>
+        <v>0.07910772582618422</v>
       </c>
       <c r="T34">
-        <v>0.7590818898177372</v>
+        <v>0.7692315433298897</v>
       </c>
       <c r="U34">
         <v>0.0641</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.161601165473667</v>
+        <v>3.065795069550222</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07106683830354343</v>
+        <v>0.0733868294432934</v>
       </c>
       <c r="C35">
-        <v>71.78288902962265</v>
+        <v>68.0849703458931</v>
       </c>
       <c r="D35">
-        <v>88.89184335697863</v>
+        <v>86.33358995589623</v>
       </c>
       <c r="E35">
-        <v>-8.357573937359099</v>
+        <v>-7.217908654711948</v>
       </c>
       <c r="F35">
-        <v>37.60895432735598</v>
+        <v>38.74861961000313</v>
       </c>
       <c r="G35">
         <v>20.5</v>
@@ -4157,45 +4157,45 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M35">
-        <v>2.410733972383519</v>
+        <v>2.786025749959225</v>
       </c>
       <c r="N35">
-        <v>4.980082354147093</v>
+        <v>4.604790576571386</v>
       </c>
       <c r="O35">
-        <v>0.7270920237054755</v>
+        <v>0.6722994241794222</v>
       </c>
       <c r="P35">
-        <v>4.252990330441618</v>
+        <v>3.932491152391964</v>
       </c>
       <c r="Q35">
-        <v>6.902990330441618</v>
+        <v>6.582491152391963</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07910772582618422</v>
+        <v>0.07956052339892941</v>
       </c>
       <c r="T35">
-        <v>0.7692315433298897</v>
+        <v>0.7796887620999865</v>
       </c>
       <c r="U35">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V35">
         <v>0.146</v>
       </c>
       <c r="W35">
-        <v>0.0547414</v>
+        <v>0.0614026</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>3.065795069550222</v>
+        <v>2.652816947811333</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0733868294432934</v>
+        <v>0.07350862458304339</v>
       </c>
       <c r="C36">
-        <v>68.0849703458931</v>
+        <v>66.81506355544704</v>
       </c>
       <c r="D36">
-        <v>86.33358995589623</v>
+        <v>86.20334844809732</v>
       </c>
       <c r="E36">
-        <v>-7.217908654711948</v>
+        <v>-6.078243372064797</v>
       </c>
       <c r="F36">
-        <v>38.74861961000313</v>
+        <v>39.88828489265028</v>
       </c>
       <c r="G36">
         <v>20.5</v>
@@ -4239,28 +4239,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M36">
-        <v>2.786025749959225</v>
+        <v>2.867967683781556</v>
       </c>
       <c r="N36">
-        <v>4.604790576571386</v>
+        <v>4.522848642749056</v>
       </c>
       <c r="O36">
-        <v>0.6722994241794222</v>
+        <v>0.660335901841362</v>
       </c>
       <c r="P36">
-        <v>3.932491152391964</v>
+        <v>3.862512740907694</v>
       </c>
       <c r="Q36">
-        <v>6.582491152391963</v>
+        <v>6.512512740907693</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07956052339892941</v>
+        <v>0.08002725320468212</v>
       </c>
       <c r="T36">
-        <v>0.7796887620999865</v>
+        <v>0.7904677414476246</v>
       </c>
       <c r="U36">
         <v>0.07190000000000001</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.652816947811333</v>
+        <v>2.577022177873866</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07350862458304339</v>
+        <v>0.07363041972279336</v>
       </c>
       <c r="C37">
-        <v>66.81506355544704</v>
+        <v>65.54554913369589</v>
       </c>
       <c r="D37">
-        <v>86.20334844809732</v>
+        <v>86.07349930899332</v>
       </c>
       <c r="E37">
-        <v>-6.078243372064797</v>
+        <v>-4.938578089417646</v>
       </c>
       <c r="F37">
-        <v>39.88828489265028</v>
+        <v>41.02795017529743</v>
       </c>
       <c r="G37">
         <v>20.5</v>
@@ -4321,28 +4321,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M37">
-        <v>2.867967683781556</v>
+        <v>2.949909617603886</v>
       </c>
       <c r="N37">
-        <v>4.522848642749056</v>
+        <v>4.440906708926725</v>
       </c>
       <c r="O37">
-        <v>0.660335901841362</v>
+        <v>0.6483723795033018</v>
       </c>
       <c r="P37">
-        <v>3.862512740907694</v>
+        <v>3.792534329423424</v>
       </c>
       <c r="Q37">
-        <v>6.512512740907693</v>
+        <v>6.442534329423424</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08002725320468212</v>
+        <v>0.08050856831686463</v>
       </c>
       <c r="T37">
-        <v>0.7904677414476246</v>
+        <v>0.8015835638998764</v>
       </c>
       <c r="U37">
         <v>0.07190000000000001</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.577022177873866</v>
+        <v>2.50543822848848</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07363041972279336</v>
+        <v>0.07498453686254335</v>
       </c>
       <c r="C38">
-        <v>65.54554913369589</v>
+        <v>62.9881402140326</v>
       </c>
       <c r="D38">
-        <v>86.07349930899332</v>
+        <v>84.65575567197718</v>
       </c>
       <c r="E38">
-        <v>-4.938578089417653</v>
+        <v>-3.798912806770502</v>
       </c>
       <c r="F38">
-        <v>41.02795017529743</v>
+        <v>42.16761545794458</v>
       </c>
       <c r="G38">
         <v>20.5</v>
@@ -4403,45 +4403,45 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M38">
-        <v>2.949909617603885</v>
+        <v>3.196305251712199</v>
       </c>
       <c r="N38">
-        <v>4.440906708926726</v>
+        <v>4.194511074818412</v>
       </c>
       <c r="O38">
-        <v>0.648372379503302</v>
+        <v>0.6123986169234882</v>
       </c>
       <c r="P38">
-        <v>3.792534329423424</v>
+        <v>3.582112457894924</v>
       </c>
       <c r="Q38">
-        <v>6.442534329423424</v>
+        <v>6.232112457894925</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08050856831686463</v>
+        <v>0.08100516327387833</v>
       </c>
       <c r="T38">
-        <v>0.8015835638998764</v>
+        <v>0.8130522696045805</v>
       </c>
       <c r="U38">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V38">
         <v>0.146</v>
       </c>
       <c r="W38">
-        <v>0.0614026</v>
+        <v>0.0647332</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.505438228488481</v>
+        <v>2.312299903950505</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07498453686254335</v>
+        <v>0.07513963800229333</v>
       </c>
       <c r="C39">
-        <v>62.9881402140326</v>
+        <v>61.68906149986271</v>
       </c>
       <c r="D39">
-        <v>84.65575567197718</v>
+        <v>84.49634224045444</v>
       </c>
       <c r="E39">
-        <v>-3.798912806770502</v>
+        <v>-2.659247524123352</v>
       </c>
       <c r="F39">
-        <v>42.16761545794458</v>
+        <v>43.30728074059173</v>
       </c>
       <c r="G39">
         <v>20.5</v>
@@ -4485,28 +4485,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M39">
-        <v>3.196305251712199</v>
+        <v>3.282691880136853</v>
       </c>
       <c r="N39">
-        <v>4.194511074818412</v>
+        <v>4.108124446393758</v>
       </c>
       <c r="O39">
-        <v>0.6123986169234882</v>
+        <v>0.5997861691734886</v>
       </c>
       <c r="P39">
-        <v>3.582112457894924</v>
+        <v>3.508338277220269</v>
       </c>
       <c r="Q39">
-        <v>6.232112457894925</v>
+        <v>6.158338277220269</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08100516327387833</v>
+        <v>0.08151777742305374</v>
       </c>
       <c r="T39">
-        <v>0.8130522696045805</v>
+        <v>0.8248909335578236</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.312299903950505</v>
+        <v>2.251449906478123</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07513963800229333</v>
+        <v>0.07529473914204331</v>
       </c>
       <c r="C40">
-        <v>61.68906149986271</v>
+        <v>60.39058203326655</v>
       </c>
       <c r="D40">
-        <v>84.49634224045444</v>
+        <v>84.33752805650543</v>
       </c>
       <c r="E40">
-        <v>-2.659247524123352</v>
+        <v>-1.519582241476201</v>
       </c>
       <c r="F40">
-        <v>43.30728074059173</v>
+        <v>44.44694602323888</v>
       </c>
       <c r="G40">
         <v>20.5</v>
@@ -4567,28 +4567,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M40">
-        <v>3.282691880136853</v>
+        <v>3.369078508561507</v>
       </c>
       <c r="N40">
-        <v>4.108124446393758</v>
+        <v>4.021737817969104</v>
       </c>
       <c r="O40">
-        <v>0.5997861691734886</v>
+        <v>0.5871737214234891</v>
       </c>
       <c r="P40">
-        <v>3.508338277220269</v>
+        <v>3.434564096545615</v>
       </c>
       <c r="Q40">
-        <v>6.158338277220269</v>
+        <v>6.084564096545614</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08151777742305374</v>
+        <v>0.08204719859351361</v>
       </c>
       <c r="T40">
-        <v>0.8248909335578236</v>
+        <v>0.8371177504275665</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.251449906478123</v>
+        <v>2.193720421696632</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07529473914204331</v>
+        <v>0.0754498402817933</v>
       </c>
       <c r="C41">
-        <v>60.39058203326655</v>
+        <v>59.09269844165516</v>
       </c>
       <c r="D41">
-        <v>84.33752805650543</v>
+        <v>84.1793097475412</v>
       </c>
       <c r="E41">
-        <v>-1.519582241476201</v>
+        <v>-0.3799169588290425</v>
       </c>
       <c r="F41">
-        <v>44.44694602323888</v>
+        <v>45.58661130588604</v>
       </c>
       <c r="G41">
         <v>20.5</v>
@@ -4649,28 +4649,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M41">
-        <v>3.369078508561507</v>
+        <v>3.455465136986162</v>
       </c>
       <c r="N41">
-        <v>4.021737817969104</v>
+        <v>3.93535118954445</v>
       </c>
       <c r="O41">
-        <v>0.5871737214234891</v>
+        <v>0.5745612736734896</v>
       </c>
       <c r="P41">
-        <v>3.434564096545615</v>
+        <v>3.36078991587096</v>
       </c>
       <c r="Q41">
-        <v>6.084564096545614</v>
+        <v>6.01078991587096</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08204719859351361</v>
+        <v>0.08259426713632215</v>
       </c>
       <c r="T41">
-        <v>0.8371177504275665</v>
+        <v>0.8497521278596342</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.193720421696632</v>
+        <v>2.138877411154216</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0754498402817933</v>
+        <v>0.07560494142154328</v>
       </c>
       <c r="C42">
-        <v>59.09269844165516</v>
+        <v>57.79540737770034</v>
       </c>
       <c r="D42">
-        <v>84.1793097475412</v>
+        <v>84.02168396623352</v>
       </c>
       <c r="E42">
-        <v>-0.3799169588290425</v>
+        <v>0.7597483238181084</v>
       </c>
       <c r="F42">
-        <v>45.58661130588604</v>
+        <v>46.72627658853319</v>
       </c>
       <c r="G42">
         <v>20.5</v>
@@ -4731,28 +4731,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M42">
-        <v>3.455465136986162</v>
+        <v>3.541851765410816</v>
       </c>
       <c r="N42">
-        <v>3.93535118954445</v>
+        <v>3.848964561119796</v>
       </c>
       <c r="O42">
-        <v>0.5745612736734896</v>
+        <v>0.5619488259234902</v>
       </c>
       <c r="P42">
-        <v>3.36078991587096</v>
+        <v>3.287015735196305</v>
       </c>
       <c r="Q42">
-        <v>6.01078991587096</v>
+        <v>5.937015735196305</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08259426713632215</v>
+        <v>0.08315988037549707</v>
       </c>
       <c r="T42">
-        <v>0.8497521278596342</v>
+        <v>0.8628147892724498</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.138877411154216</v>
+        <v>2.086709669418748</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07560494142154328</v>
+        <v>0.07576004256129326</v>
       </c>
       <c r="C43">
-        <v>57.79540737770034</v>
+        <v>56.49870551909848</v>
       </c>
       <c r="D43">
-        <v>84.02168396623352</v>
+        <v>83.86464739027882</v>
       </c>
       <c r="E43">
-        <v>0.7597483238181084</v>
+        <v>1.899413606465259</v>
       </c>
       <c r="F43">
-        <v>46.72627658853319</v>
+        <v>47.86594187118034</v>
       </c>
       <c r="G43">
         <v>20.5</v>
@@ -4813,28 +4813,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M43">
-        <v>3.541851765410816</v>
+        <v>3.62823839383547</v>
       </c>
       <c r="N43">
-        <v>3.848964561119796</v>
+        <v>3.762577932695141</v>
       </c>
       <c r="O43">
-        <v>0.5619488259234902</v>
+        <v>0.5493363781734906</v>
       </c>
       <c r="P43">
-        <v>3.287015735196305</v>
+        <v>3.213241554521651</v>
       </c>
       <c r="Q43">
-        <v>5.937015735196305</v>
+        <v>5.86324155452165</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08315988037549707</v>
+        <v>0.08374499751947112</v>
       </c>
       <c r="T43">
-        <v>0.8628147892724498</v>
+        <v>0.8763278872857075</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.086709669418748</v>
+        <v>2.037026105861158</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07576004256129326</v>
+        <v>0.08112966770104324</v>
       </c>
       <c r="C44">
-        <v>56.49870551909849</v>
+        <v>50.26235266915057</v>
       </c>
       <c r="D44">
-        <v>83.86464739027882</v>
+        <v>78.76795982297806</v>
       </c>
       <c r="E44">
-        <v>1.899413606465252</v>
+        <v>3.039078889112403</v>
       </c>
       <c r="F44">
-        <v>47.86594187118033</v>
+        <v>49.00560715382748</v>
       </c>
       <c r="G44">
         <v>20.5</v>
@@ -4895,45 +4895,45 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M44">
-        <v>3.62823839383547</v>
+        <v>4.410504643844473</v>
       </c>
       <c r="N44">
-        <v>3.762577932695142</v>
+        <v>2.980311682686138</v>
       </c>
       <c r="O44">
-        <v>0.5493363781734907</v>
+        <v>0.4351255056721762</v>
       </c>
       <c r="P44">
-        <v>3.213241554521651</v>
+        <v>2.545186177013962</v>
       </c>
       <c r="Q44">
-        <v>5.863241554521651</v>
+        <v>5.195186177013962</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08374499751947112</v>
+        <v>0.08435064508954952</v>
       </c>
       <c r="T44">
-        <v>0.8763278872857074</v>
+        <v>0.8903151290889039</v>
       </c>
       <c r="U44">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V44">
         <v>0.146</v>
       </c>
       <c r="W44">
-        <v>0.0647332</v>
+        <v>0.07686</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.037026105861159</v>
+        <v>1.675730312821598</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08112966770104324</v>
+        <v>0.08140603684079321</v>
       </c>
       <c r="C45">
-        <v>50.26235266915057</v>
+        <v>48.87707631113111</v>
       </c>
       <c r="D45">
-        <v>78.76795982297806</v>
+        <v>78.52234874760575</v>
       </c>
       <c r="E45">
-        <v>3.039078889112403</v>
+        <v>4.178744171759554</v>
       </c>
       <c r="F45">
-        <v>49.00560715382748</v>
+        <v>50.14527243647463</v>
       </c>
       <c r="G45">
         <v>20.5</v>
@@ -4977,28 +4977,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M45">
-        <v>4.410504643844473</v>
+        <v>4.513074519282717</v>
       </c>
       <c r="N45">
-        <v>2.980311682686138</v>
+        <v>2.877741807247895</v>
       </c>
       <c r="O45">
-        <v>0.4351255056721762</v>
+        <v>0.4201503038581926</v>
       </c>
       <c r="P45">
-        <v>2.545186177013962</v>
+        <v>2.457591503389702</v>
       </c>
       <c r="Q45">
-        <v>5.195186177013962</v>
+        <v>5.107591503389703</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08435064508954952</v>
+        <v>0.08497792292998788</v>
       </c>
       <c r="T45">
-        <v>0.8903151290889039</v>
+        <v>0.9048019152422144</v>
       </c>
       <c r="U45">
         <v>0.09</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.675730312821598</v>
+        <v>1.637645532984744</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08140603684079321</v>
+        <v>0.08168240598054319</v>
       </c>
       <c r="C46">
-        <v>48.87707631113111</v>
+        <v>47.49332690094252</v>
       </c>
       <c r="D46">
-        <v>78.52234874760575</v>
+        <v>78.27826462006431</v>
       </c>
       <c r="E46">
-        <v>4.178744171759554</v>
+        <v>5.318409454406705</v>
       </c>
       <c r="F46">
-        <v>50.14527243647463</v>
+        <v>51.28493771912179</v>
       </c>
       <c r="G46">
         <v>20.5</v>
@@ -5059,28 +5059,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M46">
-        <v>4.513074519282717</v>
+        <v>4.61564439472096</v>
       </c>
       <c r="N46">
-        <v>2.877741807247895</v>
+        <v>2.775171931809651</v>
       </c>
       <c r="O46">
-        <v>0.4201503038581926</v>
+        <v>0.405175102044209</v>
       </c>
       <c r="P46">
-        <v>2.457591503389702</v>
+        <v>2.369996829765442</v>
       </c>
       <c r="Q46">
-        <v>5.107591503389703</v>
+        <v>5.019996829765442</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08497792292998788</v>
+        <v>0.08562801087371488</v>
       </c>
       <c r="T46">
-        <v>0.9048019152422144</v>
+        <v>0.9198154936192818</v>
       </c>
       <c r="U46">
         <v>0.09</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.637645532984744</v>
+        <v>1.601253410029527</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08168240598054319</v>
+        <v>0.08195877512029318</v>
       </c>
       <c r="C47">
-        <v>47.49332690094252</v>
+        <v>46.1110902433096</v>
       </c>
       <c r="D47">
-        <v>78.27826462006431</v>
+        <v>78.03569324507853</v>
       </c>
       <c r="E47">
-        <v>5.318409454406705</v>
+        <v>6.458074737053856</v>
       </c>
       <c r="F47">
-        <v>51.28493771912179</v>
+        <v>52.42460300176894</v>
       </c>
       <c r="G47">
         <v>20.5</v>
@@ -5141,28 +5141,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M47">
-        <v>4.61564439472096</v>
+        <v>4.718214270159204</v>
       </c>
       <c r="N47">
-        <v>2.775171931809651</v>
+        <v>2.672602056371407</v>
       </c>
       <c r="O47">
-        <v>0.405175102044209</v>
+        <v>0.3901999002302254</v>
       </c>
       <c r="P47">
-        <v>2.369996829765442</v>
+        <v>2.282402156141182</v>
       </c>
       <c r="Q47">
-        <v>5.019996829765442</v>
+        <v>4.932402156141181</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08562801087371488</v>
+        <v>0.08630217614869105</v>
       </c>
       <c r="T47">
-        <v>0.9198154936192818</v>
+        <v>0.9353851304547591</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.601253410029527</v>
+        <v>1.566443553289755</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08195877512029318</v>
+        <v>0.08223514426004316</v>
       </c>
       <c r="C48">
-        <v>46.1110902433096</v>
+        <v>44.73035231836889</v>
       </c>
       <c r="D48">
-        <v>78.03569324507853</v>
+        <v>77.79462060278499</v>
       </c>
       <c r="E48">
-        <v>6.458074737053856</v>
+        <v>7.597740019701014</v>
       </c>
       <c r="F48">
-        <v>52.42460300176894</v>
+        <v>53.56426828441609</v>
       </c>
       <c r="G48">
         <v>20.5</v>
@@ -5223,28 +5223,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M48">
-        <v>4.718214270159204</v>
+        <v>4.820784145597449</v>
       </c>
       <c r="N48">
-        <v>2.672602056371407</v>
+        <v>2.570032180933163</v>
       </c>
       <c r="O48">
-        <v>0.3901999002302254</v>
+        <v>0.3752246984162418</v>
       </c>
       <c r="P48">
-        <v>2.282402156141182</v>
+        <v>2.194807482516921</v>
       </c>
       <c r="Q48">
-        <v>4.932402156141181</v>
+        <v>4.844807482516921</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08630217614869105</v>
+        <v>0.08700178162272293</v>
       </c>
       <c r="T48">
-        <v>0.9353851304547591</v>
+        <v>0.9515423007557262</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.566443553289755</v>
+        <v>1.533114967049547</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08223514426004316</v>
+        <v>0.08251151339979315</v>
       </c>
       <c r="C49">
-        <v>44.73035231836889</v>
+        <v>43.35109927896742</v>
       </c>
       <c r="D49">
-        <v>77.79462060278499</v>
+        <v>77.55503284603067</v>
       </c>
       <c r="E49">
-        <v>7.597740019701014</v>
+        <v>8.737405302348165</v>
       </c>
       <c r="F49">
-        <v>53.56426828441609</v>
+        <v>54.70393356706325</v>
       </c>
       <c r="G49">
         <v>20.5</v>
@@ -5305,28 +5305,28 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M49">
-        <v>4.820784145597449</v>
+        <v>4.923354021035692</v>
       </c>
       <c r="N49">
-        <v>2.570032180933163</v>
+        <v>2.467462305494919</v>
       </c>
       <c r="O49">
-        <v>0.3752246984162418</v>
+        <v>0.3602494966022582</v>
       </c>
       <c r="P49">
-        <v>2.194807482516921</v>
+        <v>2.107212808892661</v>
       </c>
       <c r="Q49">
-        <v>4.844807482516921</v>
+        <v>4.757212808892661</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08700178162272293</v>
+        <v>0.08772829499960219</v>
       </c>
       <c r="T49">
-        <v>0.9515423007557262</v>
+        <v>0.9683209006836535</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.533114967049547</v>
+        <v>1.501175071902682</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08251151339979312</v>
+        <v>0.1077553915827886</v>
       </c>
       <c r="C50">
-        <v>43.35109927896745</v>
+        <v>25.18443378845097</v>
       </c>
       <c r="D50">
-        <v>77.55503284603068</v>
+        <v>60.52803263816136</v>
       </c>
       <c r="E50">
-        <v>8.737405302348158</v>
+        <v>9.877070584995309</v>
       </c>
       <c r="F50">
-        <v>54.70393356706324</v>
+        <v>55.84359884971039</v>
       </c>
       <c r="G50">
         <v>20.5</v>
@@ -5387,45 +5387,45 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M50">
-        <v>4.923354021035691</v>
+        <v>8.197840311137487</v>
       </c>
       <c r="N50">
-        <v>2.46746230549492</v>
+        <v>-0.8070239846068752</v>
       </c>
       <c r="O50">
-        <v>0.3602494966022584</v>
+        <v>-0.1178255017526038</v>
       </c>
       <c r="P50">
-        <v>2.107212808892662</v>
+        <v>-0.6891984828542714</v>
       </c>
       <c r="Q50">
-        <v>4.757212808892662</v>
+        <v>1.960801517145728</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08772829499960218</v>
+        <v>0.08880706469861407</v>
       </c>
       <c r="T50">
-        <v>0.9683209006836534</v>
+        <v>0.99323475054536</v>
       </c>
       <c r="U50">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.146</v>
+        <v>0.1316272509245481</v>
       </c>
       <c r="W50">
-        <v>0.07686</v>
+        <v>0.1274771195642763</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y50">
-        <v>1.501175071902682</v>
+        <v>0.9015565131818362</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1077553915827886</v>
+        <v>0.1087653915827886</v>
       </c>
       <c r="C51">
-        <v>25.18443378845097</v>
+        <v>23.51771850765969</v>
       </c>
       <c r="D51">
-        <v>60.52803263816136</v>
+        <v>60.00098264001723</v>
       </c>
       <c r="E51">
-        <v>9.877070584995309</v>
+        <v>11.01673586764246</v>
       </c>
       <c r="F51">
-        <v>55.84359884971039</v>
+        <v>56.98326413235754</v>
       </c>
       <c r="G51">
         <v>20.5</v>
@@ -5469,37 +5469,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M51">
-        <v>8.197840311137487</v>
+        <v>8.365143174630088</v>
       </c>
       <c r="N51">
-        <v>-0.8070239846068752</v>
+        <v>-0.9743268480994765</v>
       </c>
       <c r="O51">
-        <v>-0.1178255017526038</v>
+        <v>-0.1422517198225235</v>
       </c>
       <c r="P51">
-        <v>-0.6891984828542714</v>
+        <v>-0.832075128276953</v>
       </c>
       <c r="Q51">
-        <v>1.960801517145728</v>
+        <v>1.817924871723047</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.08880706469861407</v>
+        <v>0.08966720599258635</v>
       </c>
       <c r="T51">
-        <v>0.99323475054536</v>
+        <v>1.013099445556267</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.1316272509245481</v>
+        <v>0.1289947059060571</v>
       </c>
       <c r="W51">
-        <v>0.1274771195642763</v>
+        <v>0.1278635771729908</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.9015565131818362</v>
+        <v>0.8835253829181995</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1087653915827886</v>
+        <v>0.1097753915827886</v>
       </c>
       <c r="C52">
-        <v>23.51771850765969</v>
+        <v>21.8601026069216</v>
       </c>
       <c r="D52">
-        <v>60.00098264001723</v>
+        <v>59.48303202192629</v>
       </c>
       <c r="E52">
-        <v>11.01673586764246</v>
+        <v>12.15640115028961</v>
       </c>
       <c r="F52">
-        <v>56.98326413235754</v>
+        <v>58.12292941500469</v>
       </c>
       <c r="G52">
         <v>20.5</v>
@@ -5551,37 +5551,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M52">
-        <v>8.365143174630088</v>
+        <v>8.532446038122689</v>
       </c>
       <c r="N52">
-        <v>-0.9743268480994765</v>
+        <v>-1.141629711592078</v>
       </c>
       <c r="O52">
-        <v>-0.1422517198225235</v>
+        <v>-0.1666779378924433</v>
       </c>
       <c r="P52">
-        <v>-0.832075128276953</v>
+        <v>-0.9749517736996344</v>
       </c>
       <c r="Q52">
-        <v>1.817924871723047</v>
+        <v>1.675048226300365</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.08966720599258635</v>
+        <v>0.09056245509447586</v>
       </c>
       <c r="T52">
-        <v>1.013099445556267</v>
+        <v>1.03377494444517</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.1289947059060571</v>
+        <v>0.1264653979471148</v>
       </c>
       <c r="W52">
-        <v>0.1278635771729908</v>
+        <v>0.1282348795813635</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8835253829181995</v>
+        <v>0.8662013558021564</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1097753915827886</v>
+        <v>0.1107853915827886</v>
       </c>
       <c r="C53">
-        <v>21.8601026069216</v>
+        <v>20.21135245540736</v>
       </c>
       <c r="D53">
-        <v>59.48303202192629</v>
+        <v>58.9739471530592</v>
       </c>
       <c r="E53">
-        <v>12.15640115028961</v>
+        <v>13.29606643293676</v>
       </c>
       <c r="F53">
-        <v>58.12292941500469</v>
+        <v>59.26259469765184</v>
       </c>
       <c r="G53">
         <v>20.5</v>
@@ -5633,37 +5633,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M53">
-        <v>8.532446038122689</v>
+        <v>8.69974890161529</v>
       </c>
       <c r="N53">
-        <v>-1.141629711592078</v>
+        <v>-1.308932575084679</v>
       </c>
       <c r="O53">
-        <v>-0.1666779378924433</v>
+        <v>-0.1911041559623631</v>
       </c>
       <c r="P53">
-        <v>-0.9749517736996344</v>
+        <v>-1.117828419122316</v>
       </c>
       <c r="Q53">
-        <v>1.675048226300365</v>
+        <v>1.532171580877684</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09056245509447586</v>
+        <v>0.09149500624227745</v>
       </c>
       <c r="T53">
-        <v>1.03377494444517</v>
+        <v>1.055311922454445</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.1264653979471148</v>
+        <v>0.1240333710635165</v>
       </c>
       <c r="W53">
-        <v>0.1282348795813635</v>
+        <v>0.1285919011278758</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8662013558021564</v>
+        <v>0.8495436374213458</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1107853915827886</v>
+        <v>0.1117953915827886</v>
       </c>
       <c r="C54">
-        <v>20.21135245540736</v>
+        <v>18.57124235252422</v>
       </c>
       <c r="D54">
-        <v>58.9739471530592</v>
+        <v>58.47350233282321</v>
       </c>
       <c r="E54">
-        <v>13.29606643293676</v>
+        <v>14.43573171558391</v>
       </c>
       <c r="F54">
-        <v>59.26259469765184</v>
+        <v>60.40225998029899</v>
       </c>
       <c r="G54">
         <v>20.5</v>
@@ -5715,37 +5715,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M54">
-        <v>8.69974890161529</v>
+        <v>8.867051765107894</v>
       </c>
       <c r="N54">
-        <v>-1.308932575084679</v>
+        <v>-1.476235438577282</v>
       </c>
       <c r="O54">
-        <v>-0.1911041559623631</v>
+        <v>-0.2155303740322832</v>
       </c>
       <c r="P54">
-        <v>-1.117828419122316</v>
+        <v>-1.260705064544999</v>
       </c>
       <c r="Q54">
-        <v>1.532171580877684</v>
+        <v>1.389294935455001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09149500624227745</v>
+        <v>0.09246724041764506</v>
       </c>
       <c r="T54">
-        <v>1.055311922454445</v>
+        <v>1.07776536761305</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.1240333710635165</v>
+        <v>0.1216931187792992</v>
       </c>
       <c r="W54">
-        <v>0.1285919011278758</v>
+        <v>0.1289354501631989</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8495436374213458</v>
+        <v>0.8335145121869807</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1117953915827886</v>
+        <v>0.1128053915827886</v>
       </c>
       <c r="C55">
-        <v>18.57124235252422</v>
+        <v>16.93955419427277</v>
       </c>
       <c r="D55">
-        <v>58.47350233282321</v>
+        <v>57.98147945721892</v>
       </c>
       <c r="E55">
-        <v>14.43573171558391</v>
+        <v>15.57539699823106</v>
       </c>
       <c r="F55">
-        <v>60.40225998029899</v>
+        <v>61.54192526294614</v>
       </c>
       <c r="G55">
         <v>20.5</v>
@@ -5797,37 +5797,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M55">
-        <v>8.867051765107894</v>
+        <v>9.034354628600495</v>
       </c>
       <c r="N55">
-        <v>-1.476235438577282</v>
+        <v>-1.643538302069883</v>
       </c>
       <c r="O55">
-        <v>-0.2155303740322832</v>
+        <v>-0.2399565921022029</v>
       </c>
       <c r="P55">
-        <v>-1.260705064544999</v>
+        <v>-1.40358170996768</v>
       </c>
       <c r="Q55">
-        <v>1.389294935455001</v>
+        <v>1.24641829003232</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09246724041764506</v>
+        <v>0.0934817456441156</v>
       </c>
       <c r="T55">
-        <v>1.07776536761305</v>
+        <v>1.101195049517682</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.1216931187792992</v>
+        <v>0.1194395425056085</v>
       </c>
       <c r="W55">
-        <v>0.1289354501631989</v>
+        <v>0.1292662751601767</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8335145121869807</v>
+        <v>0.8180790582575922</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1128053915827886</v>
+        <v>0.1138153915827886</v>
       </c>
       <c r="C56">
-        <v>16.93955419427277</v>
+        <v>15.31607715630768</v>
       </c>
       <c r="D56">
-        <v>57.98147945721892</v>
+        <v>57.49766770190099</v>
       </c>
       <c r="E56">
-        <v>15.57539699823106</v>
+        <v>16.71506228087822</v>
       </c>
       <c r="F56">
-        <v>61.54192526294614</v>
+        <v>62.6815905455933</v>
       </c>
       <c r="G56">
         <v>20.5</v>
@@ -5879,37 +5879,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M56">
-        <v>9.034354628600495</v>
+        <v>9.201657492093098</v>
       </c>
       <c r="N56">
-        <v>-1.643538302069883</v>
+        <v>-1.810841165562486</v>
       </c>
       <c r="O56">
-        <v>-0.2399565921022029</v>
+        <v>-0.264382810172123</v>
       </c>
       <c r="P56">
-        <v>-1.40358170996768</v>
+        <v>-1.546458355390363</v>
       </c>
       <c r="Q56">
-        <v>1.24641829003232</v>
+        <v>1.103541644609637</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.0934817456441156</v>
+        <v>0.09454133999176262</v>
       </c>
       <c r="T56">
-        <v>1.101195049517682</v>
+        <v>1.125666050618075</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.1194395425056085</v>
+        <v>0.1172679144600519</v>
       </c>
       <c r="W56">
-        <v>0.1292662751601767</v>
+        <v>0.1295850701572644</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8180790582575922</v>
+        <v>0.8032048935619994</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1138153915827886</v>
+        <v>0.1454720566801843</v>
       </c>
       <c r="C57">
-        <v>15.31607715630768</v>
+        <v>2.256264928173891</v>
       </c>
       <c r="D57">
-        <v>57.49766770190099</v>
+        <v>45.57752075641434</v>
       </c>
       <c r="E57">
-        <v>16.71506228087822</v>
+        <v>17.85472756352537</v>
       </c>
       <c r="F57">
-        <v>62.6815905455933</v>
+        <v>63.82125582824045</v>
       </c>
       <c r="G57">
         <v>20.5</v>
@@ -5961,45 +5961,45 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M57">
-        <v>9.201657492093098</v>
+        <v>12.81530817031068</v>
       </c>
       <c r="N57">
-        <v>-1.810841165562486</v>
+        <v>-5.424491843780071</v>
       </c>
       <c r="O57">
-        <v>-0.264382810172123</v>
+        <v>-0.7919758091918904</v>
       </c>
       <c r="P57">
-        <v>-1.546458355390363</v>
+        <v>-4.632516034588181</v>
       </c>
       <c r="Q57">
-        <v>1.103541644609637</v>
+        <v>-1.982516034588181</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09454133999176262</v>
+        <v>0.09657333657656553</v>
       </c>
       <c r="T57">
-        <v>1.125666050618075</v>
+        <v>1.172594378211675</v>
       </c>
       <c r="U57">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1172679144600519</v>
+        <v>0.08420079871144522</v>
       </c>
       <c r="W57">
-        <v>0.1295850701572644</v>
+        <v>0.1838924796187418</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y57">
-        <v>0.8032048935619994</v>
+        <v>0.5767177993934605</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1454720566801843</v>
+        <v>0.1470220566801843</v>
       </c>
       <c r="C58">
-        <v>2.256264928173891</v>
+        <v>0.6586028640439281</v>
       </c>
       <c r="D58">
-        <v>45.57752075641434</v>
+        <v>45.11952397493152</v>
       </c>
       <c r="E58">
-        <v>17.85472756352537</v>
+        <v>18.99439284617252</v>
       </c>
       <c r="F58">
-        <v>63.82125582824045</v>
+        <v>64.9609211108876</v>
       </c>
       <c r="G58">
         <v>20.5</v>
@@ -6043,37 +6043,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M58">
-        <v>12.81530817031068</v>
+        <v>13.04415295906623</v>
       </c>
       <c r="N58">
-        <v>-5.424491843780071</v>
+        <v>-5.653336632535618</v>
       </c>
       <c r="O58">
-        <v>-0.7919758091918904</v>
+        <v>-0.8253871483502002</v>
       </c>
       <c r="P58">
-        <v>-4.632516034588181</v>
+        <v>-4.827949484185417</v>
       </c>
       <c r="Q58">
-        <v>-1.982516034588181</v>
+        <v>-2.177949484185417</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09657333657656553</v>
+        <v>0.097754111845788</v>
       </c>
       <c r="T58">
-        <v>1.172594378211675</v>
+        <v>1.199864014914273</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.08420079871144522</v>
+        <v>0.0827235917165076</v>
       </c>
       <c r="W58">
-        <v>0.1838924796187418</v>
+        <v>0.1841891027833253</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5767177993934605</v>
+        <v>0.5665999432637507</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1470220566801843</v>
+        <v>0.1485720566801843</v>
       </c>
       <c r="C59">
-        <v>0.6586028640439281</v>
+        <v>-0.9299461906938689</v>
       </c>
       <c r="D59">
-        <v>45.11952397493152</v>
+        <v>44.67064020284089</v>
       </c>
       <c r="E59">
-        <v>18.99439284617252</v>
+        <v>20.13405812881967</v>
       </c>
       <c r="F59">
-        <v>64.9609211108876</v>
+        <v>66.10058639353475</v>
       </c>
       <c r="G59">
         <v>20.5</v>
@@ -6125,37 +6125,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M59">
-        <v>13.04415295906623</v>
+        <v>13.27299774782178</v>
       </c>
       <c r="N59">
-        <v>-5.653336632535618</v>
+        <v>-5.882181421291168</v>
       </c>
       <c r="O59">
-        <v>-0.8253871483502002</v>
+        <v>-0.8587984875085105</v>
       </c>
       <c r="P59">
-        <v>-4.827949484185417</v>
+        <v>-5.023382933782658</v>
       </c>
       <c r="Q59">
-        <v>-2.177949484185417</v>
+        <v>-2.373382933782658</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.097754111845788</v>
+        <v>0.09899111450878295</v>
       </c>
       <c r="T59">
-        <v>1.199864014914273</v>
+        <v>1.228432205745565</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.0827235917165076</v>
+        <v>0.08129732289380917</v>
       </c>
       <c r="W59">
-        <v>0.1841891027833253</v>
+        <v>0.1844754975629231</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5665999432637507</v>
+        <v>0.5568309787247204</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1485720566801843</v>
+        <v>0.1501220566801842</v>
       </c>
       <c r="C60">
-        <v>-0.9299461906938546</v>
+        <v>-2.509651546438917</v>
       </c>
       <c r="D60">
-        <v>44.67064020284089</v>
+        <v>44.23060012974299</v>
       </c>
       <c r="E60">
-        <v>20.13405812881966</v>
+        <v>21.27372341146682</v>
       </c>
       <c r="F60">
-        <v>66.10058639353474</v>
+        <v>67.2402516761819</v>
       </c>
       <c r="G60">
         <v>20.5</v>
@@ -6207,37 +6207,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M60">
-        <v>13.27299774782178</v>
+        <v>13.50184253657733</v>
       </c>
       <c r="N60">
-        <v>-5.882181421291165</v>
+        <v>-6.111026210046715</v>
       </c>
       <c r="O60">
-        <v>-0.85879848750851</v>
+        <v>-0.8922098266668204</v>
       </c>
       <c r="P60">
-        <v>-5.023382933782655</v>
+        <v>-5.218816383379894</v>
       </c>
       <c r="Q60">
-        <v>-2.373382933782655</v>
+        <v>-2.568816383379894</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09899111450878292</v>
+        <v>0.1002884587650947</v>
       </c>
       <c r="T60">
-        <v>1.228432205745565</v>
+        <v>1.25839396686131</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.0812973228938092</v>
+        <v>0.07991940216679547</v>
       </c>
       <c r="W60">
-        <v>0.1844754975629231</v>
+        <v>0.1847521840449075</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5568309787247205</v>
+        <v>0.5473931655259964</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1501220566801842</v>
+        <v>0.1516720566801842</v>
       </c>
       <c r="C61">
-        <v>-2.509651546438917</v>
+        <v>-4.080772005447855</v>
       </c>
       <c r="D61">
-        <v>44.23060012974299</v>
+        <v>43.79914495338118</v>
       </c>
       <c r="E61">
-        <v>21.27372341146682</v>
+        <v>22.41338869411396</v>
       </c>
       <c r="F61">
-        <v>67.2402516761819</v>
+        <v>68.37991695882904</v>
       </c>
       <c r="G61">
         <v>20.5</v>
@@ -6289,37 +6289,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M61">
-        <v>13.50184253657733</v>
+        <v>13.73068732533287</v>
       </c>
       <c r="N61">
-        <v>-6.111026210046715</v>
+        <v>-6.33987099880226</v>
       </c>
       <c r="O61">
-        <v>-0.8922098266668204</v>
+        <v>-0.9256211658251299</v>
       </c>
       <c r="P61">
-        <v>-5.218816383379894</v>
+        <v>-5.41424983297713</v>
       </c>
       <c r="Q61">
-        <v>-2.568816383379894</v>
+        <v>-2.76424983297713</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1002884587650947</v>
+        <v>0.1016506702342221</v>
       </c>
       <c r="T61">
-        <v>1.25839396686131</v>
+        <v>1.289853816032843</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.07991940216679547</v>
+        <v>0.07858741213068222</v>
       </c>
       <c r="W61">
-        <v>0.1847521840449075</v>
+        <v>0.185019647644159</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5473931655259964</v>
+        <v>0.5382699461005632</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1516720566801842</v>
+        <v>0.1532220566801842</v>
       </c>
       <c r="C62">
-        <v>-4.080772005447855</v>
+        <v>-5.643556369401033</v>
       </c>
       <c r="D62">
-        <v>43.79914495338118</v>
+        <v>43.37602587207517</v>
       </c>
       <c r="E62">
-        <v>22.41338869411396</v>
+        <v>23.55305397676112</v>
       </c>
       <c r="F62">
-        <v>68.37991695882904</v>
+        <v>69.5195822414762</v>
       </c>
       <c r="G62">
         <v>20.5</v>
@@ -6371,37 +6371,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M62">
-        <v>13.73068732533287</v>
+        <v>13.95953211408842</v>
       </c>
       <c r="N62">
-        <v>-6.33987099880226</v>
+        <v>-6.56871578755781</v>
       </c>
       <c r="O62">
-        <v>-0.9256211658251299</v>
+        <v>-0.9590325049834402</v>
       </c>
       <c r="P62">
-        <v>-5.41424983297713</v>
+        <v>-5.60968328257437</v>
       </c>
       <c r="Q62">
-        <v>-2.76424983297713</v>
+        <v>-2.95968328257437</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1016506702342221</v>
+        <v>0.1030827387017662</v>
       </c>
       <c r="T62">
-        <v>1.289853816032843</v>
+        <v>1.322926990802916</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.07858741213068222</v>
+        <v>0.07729909389903168</v>
       </c>
       <c r="W62">
-        <v>0.185019647644159</v>
+        <v>0.1852783419450744</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5382699461005632</v>
+        <v>0.5294458486235047</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1532220566801842</v>
+        <v>0.1547720566801842</v>
       </c>
       <c r="C63">
-        <v>-5.643556369401033</v>
+        <v>-7.198243917830467</v>
       </c>
       <c r="D63">
-        <v>43.37602587207517</v>
+        <v>42.96100360629288</v>
       </c>
       <c r="E63">
-        <v>23.55305397676112</v>
+        <v>24.69271925940826</v>
       </c>
       <c r="F63">
-        <v>69.5195822414762</v>
+        <v>70.65924752412334</v>
       </c>
       <c r="G63">
         <v>20.5</v>
@@ -6453,37 +6453,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M63">
-        <v>13.95953211408842</v>
+        <v>14.18837690284397</v>
       </c>
       <c r="N63">
-        <v>-6.56871578755781</v>
+        <v>-6.797560576313357</v>
       </c>
       <c r="O63">
-        <v>-0.9590325049834402</v>
+        <v>-0.99244384414175</v>
       </c>
       <c r="P63">
-        <v>-5.60968328257437</v>
+        <v>-5.805116732171607</v>
       </c>
       <c r="Q63">
-        <v>-2.95968328257437</v>
+        <v>-3.155116732171607</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1030827387017662</v>
+        <v>0.104590179193918</v>
       </c>
       <c r="T63">
-        <v>1.322926990802916</v>
+        <v>1.35774085898194</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.07729909389903168</v>
+        <v>0.07605233432001504</v>
       </c>
       <c r="W63">
-        <v>0.1852783419450744</v>
+        <v>0.185528691268541</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5294458486235047</v>
+        <v>0.5209063994521579</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1547720566801842</v>
+        <v>0.1563220566801842</v>
       </c>
       <c r="C64">
-        <v>-7.198243917830467</v>
+        <v>-8.745064859342754</v>
       </c>
       <c r="D64">
-        <v>42.96100360629288</v>
+        <v>42.55384794742775</v>
       </c>
       <c r="E64">
-        <v>24.69271925940826</v>
+        <v>25.83238454205542</v>
       </c>
       <c r="F64">
-        <v>70.65924752412334</v>
+        <v>71.7989128067705</v>
       </c>
       <c r="G64">
         <v>20.5</v>
@@ -6535,37 +6535,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M64">
-        <v>14.18837690284397</v>
+        <v>14.41722169159952</v>
       </c>
       <c r="N64">
-        <v>-6.797560576313357</v>
+        <v>-7.026405365068905</v>
       </c>
       <c r="O64">
-        <v>-0.99244384414175</v>
+        <v>-1.02585518330006</v>
       </c>
       <c r="P64">
-        <v>-5.805116732171607</v>
+        <v>-6.000550181768845</v>
       </c>
       <c r="Q64">
-        <v>-3.155116732171607</v>
+        <v>-3.350550181768845</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.104590179193918</v>
+        <v>0.1061791029559158</v>
       </c>
       <c r="T64">
-        <v>1.35774085898194</v>
+        <v>1.394436557873344</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.07605233432001504</v>
+        <v>0.07484515441017353</v>
       </c>
       <c r="W64">
-        <v>0.185528691268541</v>
+        <v>0.1857710929944371</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5209063994521579</v>
+        <v>0.5126380439052982</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1563220566801842</v>
+        <v>0.1578720566801842</v>
       </c>
       <c r="C65">
-        <v>-8.745064859342754</v>
+        <v>-10.28424075742434</v>
       </c>
       <c r="D65">
-        <v>42.55384794742775</v>
+        <v>42.1543373319933</v>
       </c>
       <c r="E65">
-        <v>25.83238454205542</v>
+        <v>26.97204982470257</v>
       </c>
       <c r="F65">
-        <v>71.7989128067705</v>
+        <v>72.93857808941765</v>
       </c>
       <c r="G65">
         <v>20.5</v>
@@ -6617,37 +6617,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M65">
-        <v>14.41722169159952</v>
+        <v>14.64606648035506</v>
       </c>
       <c r="N65">
-        <v>-7.026405365068905</v>
+        <v>-7.255250153824452</v>
       </c>
       <c r="O65">
-        <v>-1.02585518330006</v>
+        <v>-1.05926652245837</v>
       </c>
       <c r="P65">
-        <v>-6.000550181768845</v>
+        <v>-6.195983631366082</v>
       </c>
       <c r="Q65">
-        <v>-3.350550181768845</v>
+        <v>-3.545983631366082</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1061791029559158</v>
+        <v>0.1078563002602468</v>
       </c>
       <c r="T65">
-        <v>1.394436557873344</v>
+        <v>1.433170906703159</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.07484515441017353</v>
+        <v>0.07367569887251459</v>
       </c>
       <c r="W65">
-        <v>0.1857710929944371</v>
+        <v>0.1860059196663991</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5126380439052982</v>
+        <v>0.5046280744692779</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1578720566801842</v>
+        <v>0.1823361509589531</v>
       </c>
       <c r="C66">
-        <v>-10.28424075742434</v>
+        <v>-16.86416486224189</v>
       </c>
       <c r="D66">
-        <v>42.1543373319933</v>
+        <v>36.71407850982291</v>
       </c>
       <c r="E66">
-        <v>26.97204982470257</v>
+        <v>28.11171510734972</v>
       </c>
       <c r="F66">
-        <v>72.93857808941765</v>
+        <v>74.0782433720648</v>
       </c>
       <c r="G66">
         <v>20.5</v>
@@ -6699,45 +6699,45 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M66">
-        <v>14.64606648035506</v>
+        <v>17.46764978713288</v>
       </c>
       <c r="N66">
-        <v>-7.255250153824452</v>
+        <v>-10.07683346060227</v>
       </c>
       <c r="O66">
-        <v>-1.05926652245837</v>
+        <v>-1.471217685247931</v>
       </c>
       <c r="P66">
-        <v>-6.195983631366082</v>
+        <v>-8.605615775354339</v>
       </c>
       <c r="Q66">
-        <v>-3.545983631366082</v>
+        <v>-5.955615775354339</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1078563002602468</v>
+        <v>0.1100981782070218</v>
       </c>
       <c r="T66">
-        <v>1.433170906703159</v>
+        <v>1.484946378915054</v>
       </c>
       <c r="U66">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.07367569887251459</v>
+        <v>0.0617747205161127</v>
       </c>
       <c r="W66">
-        <v>0.1860059196663991</v>
+        <v>0.2212335209023006</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.5046280744692779</v>
+        <v>0.4231145240829637</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1823361509589531</v>
+        <v>0.184236150958953</v>
       </c>
       <c r="C67">
-        <v>-16.86416486224189</v>
+        <v>-18.36816698162349</v>
       </c>
       <c r="D67">
-        <v>36.71407850982291</v>
+        <v>36.34974167308847</v>
       </c>
       <c r="E67">
-        <v>28.11171510734972</v>
+        <v>29.25138038999688</v>
       </c>
       <c r="F67">
-        <v>74.0782433720648</v>
+        <v>75.21790865471196</v>
       </c>
       <c r="G67">
         <v>20.5</v>
@@ -6781,37 +6781,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M67">
-        <v>17.46764978713288</v>
+        <v>17.73638286078108</v>
       </c>
       <c r="N67">
-        <v>-10.07683346060227</v>
+        <v>-10.34556653425047</v>
       </c>
       <c r="O67">
-        <v>-1.471217685247931</v>
+        <v>-1.510452714000568</v>
       </c>
       <c r="P67">
-        <v>-8.605615775354339</v>
+        <v>-8.835113820249902</v>
       </c>
       <c r="Q67">
-        <v>-5.955615775354339</v>
+        <v>-6.185113820249901</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1100981782070218</v>
+        <v>0.1119893010954636</v>
       </c>
       <c r="T67">
-        <v>1.484946378915054</v>
+        <v>1.528621272412555</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.0617747205161127</v>
+        <v>0.0608387399022322</v>
       </c>
       <c r="W67">
-        <v>0.2212335209023006</v>
+        <v>0.2214542251310536</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.4231145240829637</v>
+        <v>0.4167036979604946</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.184236150958953</v>
+        <v>0.1861361509589531</v>
       </c>
       <c r="C68">
-        <v>-18.36816698162349</v>
+        <v>-19.86500906844377</v>
       </c>
       <c r="D68">
-        <v>36.34974167308847</v>
+        <v>35.99256486891534</v>
       </c>
       <c r="E68">
-        <v>29.25138038999688</v>
+        <v>30.39104567264403</v>
       </c>
       <c r="F68">
-        <v>75.21790865471196</v>
+        <v>76.35757393735911</v>
       </c>
       <c r="G68">
         <v>20.5</v>
@@ -6863,37 +6863,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M68">
-        <v>17.73638286078108</v>
+        <v>18.00511593442928</v>
       </c>
       <c r="N68">
-        <v>-10.34556653425047</v>
+        <v>-10.61429960789867</v>
       </c>
       <c r="O68">
-        <v>-1.510452714000568</v>
+        <v>-1.549687742753205</v>
       </c>
       <c r="P68">
-        <v>-8.835113820249902</v>
+        <v>-9.06461186514546</v>
       </c>
       <c r="Q68">
-        <v>-6.185113820249901</v>
+        <v>-6.41461186514546</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1119893010954636</v>
+        <v>0.1139950374922959</v>
       </c>
       <c r="T68">
-        <v>1.528621272412555</v>
+        <v>1.57494312915233</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.0608387399022322</v>
+        <v>0.05993069900816904</v>
       </c>
       <c r="W68">
-        <v>0.2214542251310536</v>
+        <v>0.2216683411738737</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4167036979604946</v>
+        <v>0.4104842397819798</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1861361509589531</v>
+        <v>0.188036150958953</v>
       </c>
       <c r="C69">
-        <v>-19.86500906844377</v>
+        <v>-21.35490013487163</v>
       </c>
       <c r="D69">
-        <v>35.99256486891534</v>
+        <v>35.64233908513463</v>
       </c>
       <c r="E69">
-        <v>30.39104567264403</v>
+        <v>31.53071095529118</v>
       </c>
       <c r="F69">
-        <v>76.35757393735911</v>
+        <v>77.49723922000626</v>
       </c>
       <c r="G69">
         <v>20.5</v>
@@ -6945,37 +6945,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M69">
-        <v>18.00511593442928</v>
+        <v>18.27384900807748</v>
       </c>
       <c r="N69">
-        <v>-10.61429960789867</v>
+        <v>-10.88303268154687</v>
       </c>
       <c r="O69">
-        <v>-1.549687742753205</v>
+        <v>-1.588922771505842</v>
       </c>
       <c r="P69">
-        <v>-9.06461186514546</v>
+        <v>-9.294109910041023</v>
       </c>
       <c r="Q69">
-        <v>-6.41461186514546</v>
+        <v>-6.644109910041022</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1139950374922959</v>
+        <v>0.1161261324139301</v>
       </c>
       <c r="T69">
-        <v>1.57494312915233</v>
+        <v>1.62416010193834</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.05993069900816904</v>
+        <v>0.05904936519922537</v>
       </c>
       <c r="W69">
-        <v>0.2216683411738737</v>
+        <v>0.2218761596860227</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4104842397819798</v>
+        <v>0.4044477068440094</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.188036150958953</v>
+        <v>0.1899361509589531</v>
       </c>
       <c r="C70">
-        <v>-21.35490013487163</v>
+        <v>-22.83804113629777</v>
       </c>
       <c r="D70">
-        <v>35.64233908513463</v>
+        <v>35.29886336635564</v>
       </c>
       <c r="E70">
-        <v>31.53071095529118</v>
+        <v>32.67037623793833</v>
       </c>
       <c r="F70">
-        <v>77.49723922000626</v>
+        <v>78.63690450265341</v>
       </c>
       <c r="G70">
         <v>20.5</v>
@@ -7027,37 +7027,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M70">
-        <v>18.27384900807748</v>
+        <v>18.54258208172567</v>
       </c>
       <c r="N70">
-        <v>-10.88303268154687</v>
+        <v>-11.15176575519506</v>
       </c>
       <c r="O70">
-        <v>-1.588922771505842</v>
+        <v>-1.628157800258479</v>
       </c>
       <c r="P70">
-        <v>-9.294109910041023</v>
+        <v>-9.523607954936583</v>
       </c>
       <c r="Q70">
-        <v>-6.644109910041022</v>
+        <v>-6.873607954936583</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1161261324139301</v>
+        <v>0.1183947173305085</v>
       </c>
       <c r="T70">
-        <v>1.62416010193834</v>
+        <v>1.67655236329119</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.05904936519922537</v>
+        <v>0.05819357729778733</v>
       </c>
       <c r="W70">
-        <v>0.2218761596860227</v>
+        <v>0.2220779544731818</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4044477068440094</v>
+        <v>0.3985861458752556</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1899361509589531</v>
+        <v>0.191836150958953</v>
       </c>
       <c r="C71">
-        <v>-22.83804113629777</v>
+        <v>-24.31462535583451</v>
       </c>
       <c r="D71">
-        <v>35.29886336635564</v>
+        <v>34.96194442946606</v>
       </c>
       <c r="E71">
-        <v>32.67037623793833</v>
+        <v>33.81004152058549</v>
       </c>
       <c r="F71">
-        <v>78.63690450265341</v>
+        <v>79.77656978530057</v>
       </c>
       <c r="G71">
         <v>20.5</v>
@@ -7109,37 +7109,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M71">
-        <v>18.54258208172567</v>
+        <v>18.81131515537388</v>
       </c>
       <c r="N71">
-        <v>-11.15176575519506</v>
+        <v>-11.42049882884326</v>
       </c>
       <c r="O71">
-        <v>-1.628157800258479</v>
+        <v>-1.667392829011116</v>
       </c>
       <c r="P71">
-        <v>-9.523607954936583</v>
+        <v>-9.753105999832147</v>
       </c>
       <c r="Q71">
-        <v>-6.873607954936583</v>
+        <v>-7.103105999832147</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1183947173305085</v>
+        <v>0.1208145412415255</v>
       </c>
       <c r="T71">
-        <v>1.67655236329119</v>
+        <v>1.732437442067563</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.05819357729778733</v>
+        <v>0.05736224047924749</v>
       </c>
       <c r="W71">
-        <v>0.2220779544731818</v>
+        <v>0.2222739836949934</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3985861458752556</v>
+        <v>0.3928920580770376</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.191836150958953</v>
+        <v>0.1937361509589531</v>
       </c>
       <c r="C72">
-        <v>-24.31462535583451</v>
+        <v>-25.78483876700404</v>
       </c>
       <c r="D72">
-        <v>34.96194442946606</v>
+        <v>34.63139630094367</v>
       </c>
       <c r="E72">
-        <v>33.81004152058549</v>
+        <v>34.94970680323263</v>
       </c>
       <c r="F72">
-        <v>79.77656978530057</v>
+        <v>80.91623506794771</v>
       </c>
       <c r="G72">
         <v>20.5</v>
@@ -7191,37 +7191,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M72">
-        <v>18.81131515537388</v>
+        <v>19.08004822902207</v>
       </c>
       <c r="N72">
-        <v>-11.42049882884326</v>
+        <v>-11.68923190249146</v>
       </c>
       <c r="O72">
-        <v>-1.667392829011116</v>
+        <v>-1.706627857763753</v>
       </c>
       <c r="P72">
-        <v>-9.753105999832147</v>
+        <v>-9.982604044727708</v>
       </c>
       <c r="Q72">
-        <v>-7.103105999832147</v>
+        <v>-7.332604044727708</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1208145412415255</v>
+        <v>0.1234012495601988</v>
       </c>
       <c r="T72">
-        <v>1.732437442067563</v>
+        <v>1.792176664207824</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.05736224047924749</v>
+        <v>0.0565543215992581</v>
       </c>
       <c r="W72">
-        <v>0.2222739836949934</v>
+        <v>0.2224644909668949</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3928920580770376</v>
+        <v>0.3873583671182061</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.193736150958953</v>
+        <v>0.195636150958953</v>
       </c>
       <c r="C73">
-        <v>-25.78483876700404</v>
+        <v>-27.2488603760451</v>
       </c>
       <c r="D73">
-        <v>34.63139630094367</v>
+        <v>34.30703997454975</v>
       </c>
       <c r="E73">
-        <v>34.94970680323263</v>
+        <v>36.08937208587977</v>
       </c>
       <c r="F73">
-        <v>80.91623506794771</v>
+        <v>82.05590035059485</v>
       </c>
       <c r="G73">
         <v>20.5</v>
@@ -7273,37 +7273,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M73">
-        <v>19.08004822902207</v>
+        <v>19.34878130267027</v>
       </c>
       <c r="N73">
-        <v>-11.68923190249146</v>
+        <v>-11.95796497613966</v>
       </c>
       <c r="O73">
-        <v>-1.706627857763753</v>
+        <v>-1.74586288651639</v>
       </c>
       <c r="P73">
-        <v>-9.982604044727708</v>
+        <v>-10.21210208962327</v>
       </c>
       <c r="Q73">
-        <v>-7.332604044727708</v>
+        <v>-7.562102089623266</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1234012495601987</v>
+        <v>0.1261727227587773</v>
       </c>
       <c r="T73">
-        <v>1.792176664207823</v>
+        <v>1.856182973643817</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.0565543215992581</v>
+        <v>0.05576884491037952</v>
       </c>
       <c r="W73">
-        <v>0.2224644909668949</v>
+        <v>0.2226497063701325</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3873583671182061</v>
+        <v>0.3819783897971201</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.195636150958953</v>
+        <v>0.197536150958953</v>
       </c>
       <c r="C74">
-        <v>-27.2488603760451</v>
+        <v>-28.70686254516202</v>
       </c>
       <c r="D74">
-        <v>34.30703997454975</v>
+        <v>33.98870308807999</v>
       </c>
       <c r="E74">
-        <v>36.08937208587977</v>
+        <v>37.22903736852693</v>
       </c>
       <c r="F74">
-        <v>82.05590035059485</v>
+        <v>83.19556563324201</v>
       </c>
       <c r="G74">
         <v>20.5</v>
@@ -7355,37 +7355,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M74">
-        <v>19.34878130267027</v>
+        <v>19.61751437631847</v>
       </c>
       <c r="N74">
-        <v>-11.95796497613966</v>
+        <v>-12.22669804978786</v>
       </c>
       <c r="O74">
-        <v>-1.74586288651639</v>
+        <v>-1.785097915269027</v>
       </c>
       <c r="P74">
-        <v>-10.21210208962327</v>
+        <v>-10.44160013451883</v>
       </c>
       <c r="Q74">
-        <v>-7.562102089623266</v>
+        <v>-7.791600134518829</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1261727227587773</v>
+        <v>0.1291494902683616</v>
       </c>
       <c r="T74">
-        <v>1.856182973643817</v>
+        <v>1.924930491186181</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.05576884491037952</v>
+        <v>0.05500488813078528</v>
       </c>
       <c r="W74">
-        <v>0.2226497063701325</v>
+        <v>0.2228298473787608</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3819783897971201</v>
+        <v>0.3767458091149677</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.197536150958953</v>
+        <v>0.199436150958953</v>
       </c>
       <c r="C75">
-        <v>-28.70686254516202</v>
+        <v>-30.15901129794247</v>
       </c>
       <c r="D75">
-        <v>33.98870308807999</v>
+        <v>33.67621961794669</v>
       </c>
       <c r="E75">
-        <v>37.22903736852693</v>
+        <v>38.36870265117408</v>
       </c>
       <c r="F75">
-        <v>83.19556563324201</v>
+        <v>84.33523091588916</v>
       </c>
       <c r="G75">
         <v>20.5</v>
@@ -7437,37 +7437,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M75">
-        <v>19.61751437631847</v>
+        <v>19.88624744996666</v>
       </c>
       <c r="N75">
-        <v>-12.22669804978786</v>
+        <v>-12.49543112343605</v>
       </c>
       <c r="O75">
-        <v>-1.785097915269027</v>
+        <v>-1.824332944021664</v>
       </c>
       <c r="P75">
-        <v>-10.44160013451883</v>
+        <v>-10.67109817941439</v>
       </c>
       <c r="Q75">
-        <v>-7.791600134518829</v>
+        <v>-8.021098179414389</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1291494902683616</v>
+        <v>0.1323552398940678</v>
       </c>
       <c r="T75">
-        <v>1.924930491186181</v>
+        <v>1.998966279308726</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.05500488813078528</v>
+        <v>0.05426157883172061</v>
       </c>
       <c r="W75">
-        <v>0.2228298473787608</v>
+        <v>0.2230051197114803</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3767458091149677</v>
+        <v>0.371654649532333</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.199436150958953</v>
+        <v>0.201336150958953</v>
       </c>
       <c r="C76">
-        <v>-30.15901129794247</v>
+        <v>-31.60546660808119</v>
       </c>
       <c r="D76">
-        <v>33.67621961794669</v>
+        <v>33.36942959045512</v>
       </c>
       <c r="E76">
-        <v>38.36870265117408</v>
+        <v>39.50836793382123</v>
       </c>
       <c r="F76">
-        <v>84.33523091588916</v>
+        <v>85.47489619853631</v>
       </c>
       <c r="G76">
         <v>20.5</v>
@@ -7519,37 +7519,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M76">
-        <v>19.88624744996666</v>
+        <v>20.15498052361486</v>
       </c>
       <c r="N76">
-        <v>-12.49543112343605</v>
+        <v>-12.76416419708425</v>
       </c>
       <c r="O76">
-        <v>-1.824332944021664</v>
+        <v>-1.863567972774301</v>
       </c>
       <c r="P76">
-        <v>-10.67109817941439</v>
+        <v>-10.90059622430995</v>
       </c>
       <c r="Q76">
-        <v>-8.021098179414389</v>
+        <v>-8.250596224309952</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1323552398940678</v>
+        <v>0.1358174494898305</v>
       </c>
       <c r="T76">
-        <v>1.998966279308726</v>
+        <v>2.078924930481076</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.05426157883172061</v>
+        <v>0.05353809111396433</v>
       </c>
       <c r="W76">
-        <v>0.2230051197114803</v>
+        <v>0.2231757181153272</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.371654649532333</v>
+        <v>0.3666992542052352</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.201336150958953</v>
+        <v>0.2032361509589531</v>
       </c>
       <c r="C77">
-        <v>-31.60546660808119</v>
+        <v>-33.04638267246443</v>
       </c>
       <c r="D77">
-        <v>33.36942959045512</v>
+        <v>33.06817880871903</v>
       </c>
       <c r="E77">
-        <v>39.50836793382123</v>
+        <v>40.64803321646838</v>
       </c>
       <c r="F77">
-        <v>85.47489619853631</v>
+        <v>86.61456148118346</v>
       </c>
       <c r="G77">
         <v>20.5</v>
@@ -7601,37 +7601,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M77">
-        <v>20.15498052361486</v>
+        <v>20.42371359726306</v>
       </c>
       <c r="N77">
-        <v>-12.76416419708425</v>
+        <v>-13.03289727073245</v>
       </c>
       <c r="O77">
-        <v>-1.863567972774301</v>
+        <v>-1.902803001526937</v>
       </c>
       <c r="P77">
-        <v>-10.90059622430995</v>
+        <v>-11.13009426920551</v>
       </c>
       <c r="Q77">
-        <v>-8.250596224309952</v>
+        <v>-8.480094269205511</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1358174494898305</v>
+        <v>0.1395681765519068</v>
       </c>
       <c r="T77">
-        <v>2.078924930481076</v>
+        <v>2.165546802584454</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.05353809111396433</v>
+        <v>0.05283364254667534</v>
       </c>
       <c r="W77">
-        <v>0.2231757181153272</v>
+        <v>0.223341827087494</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3666992542052352</v>
+        <v>0.3618742640183242</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2032361509589531</v>
+        <v>0.205136150958953</v>
       </c>
       <c r="C78">
-        <v>-33.04638267246443</v>
+        <v>-34.4819081695949</v>
       </c>
       <c r="D78">
-        <v>33.06817880871903</v>
+        <v>32.77231859423572</v>
       </c>
       <c r="E78">
-        <v>40.64803321646838</v>
+        <v>41.78769849911554</v>
       </c>
       <c r="F78">
-        <v>86.61456148118346</v>
+        <v>87.75422676383062</v>
       </c>
       <c r="G78">
         <v>20.5</v>
@@ -7683,37 +7683,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M78">
-        <v>20.42371359726306</v>
+        <v>20.69244667091126</v>
       </c>
       <c r="N78">
-        <v>-13.03289727073245</v>
+        <v>-13.30163034438065</v>
       </c>
       <c r="O78">
-        <v>-1.902803001526937</v>
+        <v>-1.942038030279575</v>
       </c>
       <c r="P78">
-        <v>-11.13009426920551</v>
+        <v>-11.35959231410107</v>
       </c>
       <c r="Q78">
-        <v>-8.480094269205511</v>
+        <v>-8.709592314101073</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1395681765519068</v>
+        <v>0.1436450537932941</v>
       </c>
       <c r="T78">
-        <v>2.165546802584454</v>
+        <v>2.259701011392473</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.05283364254667534</v>
+        <v>0.05214749134477046</v>
       </c>
       <c r="W78">
-        <v>0.223341827087494</v>
+        <v>0.2235036215409031</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3618742640183242</v>
+        <v>0.3571745982518525</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.205136150958953</v>
+        <v>0.2070361509589531</v>
       </c>
       <c r="C79">
-        <v>-34.4819081695949</v>
+        <v>-35.9121865042668</v>
       </c>
       <c r="D79">
-        <v>32.77231859423572</v>
+        <v>32.48170554221096</v>
       </c>
       <c r="E79">
-        <v>41.78769849911554</v>
+        <v>42.92736378176268</v>
       </c>
       <c r="F79">
-        <v>87.75422676383062</v>
+        <v>88.89389204647776</v>
       </c>
       <c r="G79">
         <v>20.5</v>
@@ -7765,37 +7765,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M79">
-        <v>20.69244667091126</v>
+        <v>20.96117974455946</v>
       </c>
       <c r="N79">
-        <v>-13.30163034438065</v>
+        <v>-13.57036341802884</v>
       </c>
       <c r="O79">
-        <v>-1.942038030279575</v>
+        <v>-1.981273059032211</v>
       </c>
       <c r="P79">
-        <v>-11.35959231410107</v>
+        <v>-11.58909035899663</v>
       </c>
       <c r="Q79">
-        <v>-8.709592314101073</v>
+        <v>-8.939090358996632</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1436450537932941</v>
+        <v>0.1480925562384438</v>
       </c>
       <c r="T79">
-        <v>2.259701011392473</v>
+        <v>2.362414693728495</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.05214749134477046</v>
+        <v>0.05147893376342726</v>
       </c>
       <c r="W79">
-        <v>0.2235036215409031</v>
+        <v>0.2236612674185839</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3571745982518525</v>
+        <v>0.3525954367358032</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2070361509589531</v>
+        <v>0.2089361509589531</v>
       </c>
       <c r="C80">
-        <v>-35.9121865042668</v>
+        <v>-37.33735603933734</v>
       </c>
       <c r="D80">
-        <v>32.48170554221096</v>
+        <v>32.19620128978757</v>
       </c>
       <c r="E80">
-        <v>42.92736378176268</v>
+        <v>44.06702906440984</v>
       </c>
       <c r="F80">
-        <v>88.89389204647776</v>
+        <v>90.03355732912492</v>
       </c>
       <c r="G80">
         <v>20.5</v>
@@ -7847,37 +7847,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M80">
-        <v>20.96117974455946</v>
+        <v>21.22991281820766</v>
       </c>
       <c r="N80">
-        <v>-13.57036341802884</v>
+        <v>-13.83909649167704</v>
       </c>
       <c r="O80">
-        <v>-1.981273059032211</v>
+        <v>-2.020508087784848</v>
       </c>
       <c r="P80">
-        <v>-11.58909035899663</v>
+        <v>-11.8185884038922</v>
       </c>
       <c r="Q80">
-        <v>-8.939090358996632</v>
+        <v>-9.168588403892196</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1480925562384438</v>
+        <v>0.1529636303450363</v>
       </c>
       <c r="T80">
-        <v>2.362414693728495</v>
+        <v>2.47491063152509</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.05147893376342726</v>
+        <v>0.05082730169047248</v>
       </c>
       <c r="W80">
-        <v>0.2236612674185839</v>
+        <v>0.2238149222613866</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3525954367358032</v>
+        <v>0.3481322033594005</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2089361509589531</v>
+        <v>0.210836150958953</v>
       </c>
       <c r="C81">
-        <v>-37.33735603933734</v>
+        <v>-38.7575503153814</v>
       </c>
       <c r="D81">
-        <v>32.19620128978757</v>
+        <v>31.91567229639067</v>
       </c>
       <c r="E81">
-        <v>44.06702906440984</v>
+        <v>45.206694347057</v>
       </c>
       <c r="F81">
-        <v>90.03355732912492</v>
+        <v>91.17322261177208</v>
       </c>
       <c r="G81">
         <v>20.5</v>
@@ -7929,37 +7929,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M81">
-        <v>21.22991281820766</v>
+        <v>21.49864589185585</v>
       </c>
       <c r="N81">
-        <v>-13.83909649167704</v>
+        <v>-14.10782956532524</v>
       </c>
       <c r="O81">
-        <v>-2.020508087784848</v>
+        <v>-2.059743116537486</v>
       </c>
       <c r="P81">
-        <v>-11.8185884038922</v>
+        <v>-12.04808644878776</v>
       </c>
       <c r="Q81">
-        <v>-9.168588403892196</v>
+        <v>-9.398086448787756</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1529636303450363</v>
+        <v>0.1583218118622882</v>
       </c>
       <c r="T81">
-        <v>2.47491063152509</v>
+        <v>2.598656163101345</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.05082730169047248</v>
+        <v>0.05019196041934156</v>
       </c>
       <c r="W81">
-        <v>0.2238149222613866</v>
+        <v>0.2239647357331193</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3481322033594005</v>
+        <v>0.343780550817408</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.210836150958953</v>
+        <v>0.2127361509589531</v>
       </c>
       <c r="C82">
-        <v>-38.7575503153814</v>
+        <v>-40.17289825896218</v>
       </c>
       <c r="D82">
-        <v>31.91567229639067</v>
+        <v>31.63998963545704</v>
       </c>
       <c r="E82">
-        <v>45.206694347057</v>
+        <v>46.34635962970414</v>
       </c>
       <c r="F82">
-        <v>91.17322261177208</v>
+        <v>92.31288789441922</v>
       </c>
       <c r="G82">
         <v>20.5</v>
@@ -8011,37 +8011,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M82">
-        <v>21.49864589185585</v>
+        <v>21.76737896550405</v>
       </c>
       <c r="N82">
-        <v>-14.10782956532524</v>
+        <v>-14.37656263897344</v>
       </c>
       <c r="O82">
-        <v>-2.059743116537486</v>
+        <v>-2.098978145290122</v>
       </c>
       <c r="P82">
-        <v>-12.04808644878776</v>
+        <v>-12.27758449368332</v>
       </c>
       <c r="Q82">
-        <v>-9.398086448787756</v>
+        <v>-9.627584493683321</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1583218118622882</v>
+        <v>0.1642440124866191</v>
       </c>
       <c r="T82">
-        <v>2.598656163101345</v>
+        <v>2.735427540106679</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.05019196041934156</v>
+        <v>0.04957230658700401</v>
       </c>
       <c r="W82">
-        <v>0.2239647357331193</v>
+        <v>0.2241108501067845</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.343780550817408</v>
+        <v>0.3395363464863289</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2127361509589531</v>
+        <v>0.2146361509589531</v>
       </c>
       <c r="C83">
-        <v>-40.17289825896218</v>
+        <v>-41.58352438020027</v>
       </c>
       <c r="D83">
-        <v>31.63998963545704</v>
+        <v>31.36902879686611</v>
       </c>
       <c r="E83">
-        <v>46.34635962970414</v>
+        <v>47.4860249123513</v>
       </c>
       <c r="F83">
-        <v>92.31288789441922</v>
+        <v>93.45255317706638</v>
       </c>
       <c r="G83">
         <v>20.5</v>
@@ -8093,37 +8093,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M83">
-        <v>21.76737896550405</v>
+        <v>22.03611203915225</v>
       </c>
       <c r="N83">
-        <v>-14.37656263897344</v>
+        <v>-14.64529571262164</v>
       </c>
       <c r="O83">
-        <v>-2.098978145290122</v>
+        <v>-2.13821317404276</v>
       </c>
       <c r="P83">
-        <v>-12.27758449368332</v>
+        <v>-12.50708253857888</v>
       </c>
       <c r="Q83">
-        <v>-9.627584493683321</v>
+        <v>-9.857082538578883</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1642440124866191</v>
+        <v>0.1708242354025425</v>
       </c>
       <c r="T83">
-        <v>2.735427540106679</v>
+        <v>2.887395736779272</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.04957230658700401</v>
+        <v>0.04896776626277225</v>
       </c>
       <c r="W83">
-        <v>0.2241108501067845</v>
+        <v>0.2242534007152383</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3395363464863289</v>
+        <v>0.3353956593340566</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2146361509589531</v>
+        <v>0.2165361509589531</v>
       </c>
       <c r="C84">
-        <v>-41.58352438020027</v>
+        <v>-42.98954896027713</v>
       </c>
       <c r="D84">
-        <v>31.36902879686611</v>
+        <v>31.10266949943639</v>
       </c>
       <c r="E84">
-        <v>47.4860249123513</v>
+        <v>48.62569019499844</v>
       </c>
       <c r="F84">
-        <v>93.45255317706638</v>
+        <v>94.59221845971352</v>
       </c>
       <c r="G84">
         <v>20.5</v>
@@ -8175,37 +8175,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M84">
-        <v>22.03611203915225</v>
+        <v>22.30484511280045</v>
       </c>
       <c r="N84">
-        <v>-14.64529571262164</v>
+        <v>-14.91402878626984</v>
       </c>
       <c r="O84">
-        <v>-2.13821317404276</v>
+        <v>-2.177448202795397</v>
       </c>
       <c r="P84">
-        <v>-12.50708253857888</v>
+        <v>-12.73658058347444</v>
       </c>
       <c r="Q84">
-        <v>-9.857082538578883</v>
+        <v>-10.08658058347444</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1708242354025425</v>
+        <v>0.1781786021909273</v>
       </c>
       <c r="T84">
-        <v>2.887395736779272</v>
+        <v>3.057242544825112</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.04896776626277225</v>
+        <v>0.04837779317526898</v>
       </c>
       <c r="W84">
-        <v>0.2242534007152383</v>
+        <v>0.2243925163692716</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3353956593340566</v>
+        <v>0.331354747775815</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2165361509589531</v>
+        <v>0.2184361509589531</v>
       </c>
       <c r="C85">
-        <v>-42.98954896027713</v>
+        <v>-44.39108822946636</v>
       </c>
       <c r="D85">
-        <v>31.10266949943639</v>
+        <v>30.84079551289432</v>
       </c>
       <c r="E85">
-        <v>48.62569019499844</v>
+        <v>49.7653554776456</v>
       </c>
       <c r="F85">
-        <v>94.59221845971352</v>
+        <v>95.73188374236068</v>
       </c>
       <c r="G85">
         <v>20.5</v>
@@ -8257,37 +8257,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M85">
-        <v>22.30484511280045</v>
+        <v>22.57357818644865</v>
       </c>
       <c r="N85">
-        <v>-14.91402878626984</v>
+        <v>-15.18276185991804</v>
       </c>
       <c r="O85">
-        <v>-2.177448202795397</v>
+        <v>-2.216683231548033</v>
       </c>
       <c r="P85">
-        <v>-12.73658058347444</v>
+        <v>-12.96607862837</v>
       </c>
       <c r="Q85">
-        <v>-10.08658058347444</v>
+        <v>-10.31607862837</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1781786021909273</v>
+        <v>0.1864522648278603</v>
       </c>
       <c r="T85">
-        <v>3.057242544825112</v>
+        <v>3.248320203876682</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.04837779317526898</v>
+        <v>0.04780186706603958</v>
       </c>
       <c r="W85">
-        <v>0.2243925163692716</v>
+        <v>0.2245283197458279</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.331354747775815</v>
+        <v>0.3274100483975314</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.218436150958953</v>
+        <v>0.220336150958953</v>
       </c>
       <c r="C86">
-        <v>-44.39108822946634</v>
+        <v>-45.78825453624606</v>
       </c>
       <c r="D86">
-        <v>30.84079551289432</v>
+        <v>30.58329448876175</v>
       </c>
       <c r="E86">
-        <v>49.76535547764558</v>
+        <v>50.90502076029273</v>
       </c>
       <c r="F86">
-        <v>95.73188374236067</v>
+        <v>96.87154902500781</v>
       </c>
       <c r="G86">
         <v>20.5</v>
@@ -8339,37 +8339,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M86">
-        <v>22.57357818644865</v>
+        <v>22.84231126009684</v>
       </c>
       <c r="N86">
-        <v>-15.18276185991803</v>
+        <v>-15.45149493356623</v>
       </c>
       <c r="O86">
-        <v>-2.216683231548033</v>
+        <v>-2.25591826030067</v>
       </c>
       <c r="P86">
-        <v>-12.96607862837</v>
+        <v>-13.19557667326556</v>
       </c>
       <c r="Q86">
-        <v>-10.31607862837</v>
+        <v>-10.54557667326556</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1864522648278602</v>
+        <v>0.1958290824830509</v>
       </c>
       <c r="T86">
-        <v>3.24832020387668</v>
+        <v>3.464874884135125</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04780186706603959</v>
+        <v>0.04723949215938031</v>
       </c>
       <c r="W86">
-        <v>0.2245283197458279</v>
+        <v>0.2246609277488181</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3274100483975314</v>
+        <v>0.3235581654752075</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.220336150958953</v>
+        <v>0.222236150958953</v>
       </c>
       <c r="C87">
-        <v>-45.78825453624606</v>
+        <v>-47.18115650800988</v>
       </c>
       <c r="D87">
-        <v>30.58329448876175</v>
+        <v>30.33005779964509</v>
       </c>
       <c r="E87">
-        <v>50.90502076029273</v>
+        <v>52.04468604293989</v>
       </c>
       <c r="F87">
-        <v>96.87154902500781</v>
+        <v>98.01121430765497</v>
       </c>
       <c r="G87">
         <v>20.5</v>
@@ -8421,37 +8421,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M87">
-        <v>22.84231126009684</v>
+        <v>23.11104433374504</v>
       </c>
       <c r="N87">
-        <v>-15.45149493356623</v>
+        <v>-15.72022800721443</v>
       </c>
       <c r="O87">
-        <v>-2.25591826030067</v>
+        <v>-2.295153289053307</v>
       </c>
       <c r="P87">
-        <v>-13.19557667326556</v>
+        <v>-13.42507471816112</v>
       </c>
       <c r="Q87">
-        <v>-10.54557667326556</v>
+        <v>-10.77507471816112</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1958290824830509</v>
+        <v>0.2065454455175545</v>
       </c>
       <c r="T87">
-        <v>3.464874884135125</v>
+        <v>3.712365947287634</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04723949215938031</v>
+        <v>0.04669019573892239</v>
       </c>
       <c r="W87">
-        <v>0.2246609277488181</v>
+        <v>0.2247904518447621</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3235581654752075</v>
+        <v>0.3197958612254959</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.222236150958953</v>
+        <v>0.2241361509589531</v>
       </c>
       <c r="C88">
-        <v>-47.18115650800988</v>
+        <v>-48.56989920385871</v>
       </c>
       <c r="D88">
-        <v>30.33005779964509</v>
+        <v>30.08098038644341</v>
       </c>
       <c r="E88">
-        <v>52.04468604293989</v>
+        <v>53.18435132558704</v>
       </c>
       <c r="F88">
-        <v>98.01121430765497</v>
+        <v>99.15087959030213</v>
       </c>
       <c r="G88">
         <v>20.5</v>
@@ -8503,37 +8503,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M88">
-        <v>23.11104433374504</v>
+        <v>23.37977740739324</v>
       </c>
       <c r="N88">
-        <v>-15.72022800721443</v>
+        <v>-15.98896108086263</v>
       </c>
       <c r="O88">
-        <v>-2.295153289053307</v>
+        <v>-2.334388317805944</v>
       </c>
       <c r="P88">
-        <v>-13.42507471816112</v>
+        <v>-13.65457276305669</v>
       </c>
       <c r="Q88">
-        <v>-10.77507471816112</v>
+        <v>-11.00457276305669</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2065454455175545</v>
+        <v>0.2189104797881356</v>
       </c>
       <c r="T88">
-        <v>3.712365947287634</v>
+        <v>3.997932558617452</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04669019573892239</v>
+        <v>0.04615352682238304</v>
       </c>
       <c r="W88">
-        <v>0.2247904518447621</v>
+        <v>0.2249169983752821</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3197958612254959</v>
+        <v>0.316120046728651</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2241361509589531</v>
+        <v>0.2260361509589531</v>
       </c>
       <c r="C89">
-        <v>-48.56989920385871</v>
+        <v>-49.95458425992567</v>
       </c>
       <c r="D89">
-        <v>30.08098038644341</v>
+        <v>29.8359606130236</v>
       </c>
       <c r="E89">
-        <v>53.18435132558704</v>
+        <v>54.32401660823419</v>
       </c>
       <c r="F89">
-        <v>99.15087959030213</v>
+        <v>100.2905448729493</v>
       </c>
       <c r="G89">
         <v>20.5</v>
@@ -8585,37 +8585,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M89">
-        <v>23.37977740739324</v>
+        <v>23.64851048104144</v>
       </c>
       <c r="N89">
-        <v>-15.98896108086263</v>
+        <v>-16.25769415451083</v>
       </c>
       <c r="O89">
-        <v>-2.334388317805944</v>
+        <v>-2.37362334655858</v>
       </c>
       <c r="P89">
-        <v>-13.65457276305669</v>
+        <v>-13.88407080795225</v>
       </c>
       <c r="Q89">
-        <v>-11.00457276305669</v>
+        <v>-11.23407080795224</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2189104797881356</v>
+        <v>0.2333363531038136</v>
       </c>
       <c r="T89">
-        <v>3.997932558617452</v>
+        <v>4.331093605168907</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04615352682238304</v>
+        <v>0.04562905492667416</v>
       </c>
       <c r="W89">
-        <v>0.2249169983752821</v>
+        <v>0.2250406688482902</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.316120046728651</v>
+        <v>0.312527773470371</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2260361509589531</v>
+        <v>0.2279361509589531</v>
       </c>
       <c r="C90">
-        <v>-49.95458425992567</v>
+        <v>-51.33531002765589</v>
       </c>
       <c r="D90">
-        <v>29.8359606130236</v>
+        <v>29.59490012794054</v>
       </c>
       <c r="E90">
-        <v>54.32401660823419</v>
+        <v>55.46368189088135</v>
       </c>
       <c r="F90">
-        <v>100.2905448729493</v>
+        <v>101.4302101555964</v>
       </c>
       <c r="G90">
         <v>20.5</v>
@@ -8667,37 +8667,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M90">
-        <v>23.64851048104144</v>
+        <v>23.91724355468964</v>
       </c>
       <c r="N90">
-        <v>-16.25769415451083</v>
+        <v>-16.52642722815903</v>
       </c>
       <c r="O90">
-        <v>-2.37362334655858</v>
+        <v>-2.412858375311218</v>
       </c>
       <c r="P90">
-        <v>-13.88407080795225</v>
+        <v>-14.11356885284781</v>
       </c>
       <c r="Q90">
-        <v>-11.23407080795224</v>
+        <v>-11.46356885284781</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2333363531038136</v>
+        <v>0.2503851124768876</v>
       </c>
       <c r="T90">
-        <v>4.331093605168907</v>
+        <v>4.724829387456991</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04562905492667416</v>
+        <v>0.04511636891626208</v>
       </c>
       <c r="W90">
-        <v>0.2250406688482902</v>
+        <v>0.2251615602095454</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.312527773470371</v>
+        <v>0.3090162254538499</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2279361509589531</v>
+        <v>0.229836150958953</v>
       </c>
       <c r="C91">
-        <v>-51.33531002765589</v>
+        <v>-52.71217170543656</v>
       </c>
       <c r="D91">
-        <v>29.59490012794054</v>
+        <v>29.35770373280701</v>
       </c>
       <c r="E91">
-        <v>55.46368189088135</v>
+        <v>56.60334717352849</v>
       </c>
       <c r="F91">
-        <v>101.4302101555964</v>
+        <v>102.5698754382436</v>
       </c>
       <c r="G91">
         <v>20.5</v>
@@ -8749,37 +8749,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M91">
-        <v>23.91724355468964</v>
+        <v>24.18597662833783</v>
       </c>
       <c r="N91">
-        <v>-16.52642722815903</v>
+        <v>-16.79516030180722</v>
       </c>
       <c r="O91">
-        <v>-2.412858375311218</v>
+        <v>-2.452093404063854</v>
       </c>
       <c r="P91">
-        <v>-14.11356885284781</v>
+        <v>-14.34306689774337</v>
       </c>
       <c r="Q91">
-        <v>-11.46356885284781</v>
+        <v>-11.69306689774337</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2503851124768876</v>
+        <v>0.2708436237245764</v>
       </c>
       <c r="T91">
-        <v>4.724829387456991</v>
+        <v>5.19731232620269</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.04511636891626208</v>
+        <v>0.04461507592830362</v>
       </c>
       <c r="W91">
-        <v>0.2251615602095454</v>
+        <v>0.225279765096106</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3090162254538499</v>
+        <v>0.305582711837696</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.229836150958953</v>
+        <v>0.231736150958953</v>
       </c>
       <c r="C92">
-        <v>-52.71217170543656</v>
+        <v>-54.08526146394762</v>
       </c>
       <c r="D92">
-        <v>29.35770373280701</v>
+        <v>29.1242792569431</v>
       </c>
       <c r="E92">
-        <v>56.60334717352849</v>
+        <v>57.74301245617565</v>
       </c>
       <c r="F92">
-        <v>102.5698754382436</v>
+        <v>103.7095407208907</v>
       </c>
       <c r="G92">
         <v>20.5</v>
@@ -8831,37 +8831,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M92">
-        <v>24.18597662833783</v>
+        <v>24.45470970198603</v>
       </c>
       <c r="N92">
-        <v>-16.79516030180722</v>
+        <v>-17.06389337545542</v>
       </c>
       <c r="O92">
-        <v>-2.452093404063854</v>
+        <v>-2.491328432816491</v>
       </c>
       <c r="P92">
-        <v>-14.34306689774337</v>
+        <v>-14.57256494263893</v>
       </c>
       <c r="Q92">
-        <v>-11.69306689774337</v>
+        <v>-11.92256494263893</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2708436237245764</v>
+        <v>0.2958484708050849</v>
       </c>
       <c r="T92">
-        <v>5.19731232620269</v>
+        <v>5.774791473558545</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.04461507592830362</v>
+        <v>0.04412480036865193</v>
       </c>
       <c r="W92">
-        <v>0.225279765096106</v>
+        <v>0.2253953720730719</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.305582711837696</v>
+        <v>0.3022246600592599</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.231736150958953</v>
+        <v>0.233636150958953</v>
       </c>
       <c r="C93">
-        <v>-54.08526146394762</v>
+        <v>-55.45466856557935</v>
       </c>
       <c r="D93">
-        <v>29.1242792569431</v>
+        <v>28.89453743795852</v>
       </c>
       <c r="E93">
-        <v>57.74301245617565</v>
+        <v>58.88267773882279</v>
       </c>
       <c r="F93">
-        <v>103.7095407208907</v>
+        <v>104.8492060035379</v>
       </c>
       <c r="G93">
         <v>20.5</v>
@@ -8913,37 +8913,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M93">
-        <v>24.45470970198603</v>
+        <v>24.72344277563423</v>
       </c>
       <c r="N93">
-        <v>-17.06389337545542</v>
+        <v>-17.33262644910362</v>
       </c>
       <c r="O93">
-        <v>-2.491328432816491</v>
+        <v>-2.530563461569129</v>
       </c>
       <c r="P93">
-        <v>-14.57256494263893</v>
+        <v>-14.80206298753449</v>
       </c>
       <c r="Q93">
-        <v>-11.92256494263893</v>
+        <v>-12.15206298753449</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2958484708050849</v>
+        <v>0.3271045296557206</v>
       </c>
       <c r="T93">
-        <v>5.774791473558545</v>
+        <v>6.496640407753364</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.04412480036865193</v>
+        <v>0.0436451829733405</v>
       </c>
       <c r="W93">
-        <v>0.2253953720730719</v>
+        <v>0.2255084658548863</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3022246600592599</v>
+        <v>0.2989396094064417</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.233636150958953</v>
+        <v>0.2355361509589531</v>
       </c>
       <c r="C94">
-        <v>-55.45466856557935</v>
+        <v>-56.82047947824238</v>
       </c>
       <c r="D94">
-        <v>28.89453743795852</v>
+        <v>28.66839180794265</v>
       </c>
       <c r="E94">
-        <v>58.88267773882279</v>
+        <v>60.02234302146995</v>
       </c>
       <c r="F94">
-        <v>104.8492060035379</v>
+        <v>105.988871286185</v>
       </c>
       <c r="G94">
         <v>20.5</v>
@@ -8995,37 +8995,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M94">
-        <v>24.72344277563423</v>
+        <v>24.99217584928243</v>
       </c>
       <c r="N94">
-        <v>-17.33262644910362</v>
+        <v>-17.60135952275182</v>
       </c>
       <c r="O94">
-        <v>-2.530563461569129</v>
+        <v>-2.569798490321766</v>
       </c>
       <c r="P94">
-        <v>-14.80206298753449</v>
+        <v>-15.03156103243006</v>
       </c>
       <c r="Q94">
-        <v>-12.15206298753449</v>
+        <v>-12.38156103243005</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3271045296557206</v>
+        <v>0.3672908910351093</v>
       </c>
       <c r="T94">
-        <v>6.496640407753364</v>
+        <v>7.424731894575274</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0436451829733405</v>
+        <v>0.0431758799306164</v>
       </c>
       <c r="W94">
-        <v>0.2255084658548863</v>
+        <v>0.2256191275123607</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2989396094064417</v>
+        <v>0.2957252050042219</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2355361509589531</v>
+        <v>0.237436150958953</v>
       </c>
       <c r="C95">
-        <v>-56.82047947824238</v>
+        <v>-58.18277798387457</v>
       </c>
       <c r="D95">
-        <v>28.66839180794265</v>
+        <v>28.44575858495762</v>
       </c>
       <c r="E95">
-        <v>60.02234302146995</v>
+        <v>61.16200830411711</v>
       </c>
       <c r="F95">
-        <v>105.988871286185</v>
+        <v>107.1285365688322</v>
       </c>
       <c r="G95">
         <v>20.5</v>
@@ -9077,37 +9077,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M95">
-        <v>24.99217584928243</v>
+        <v>25.26090892293063</v>
       </c>
       <c r="N95">
-        <v>-17.60135952275182</v>
+        <v>-17.87009259640002</v>
       </c>
       <c r="O95">
-        <v>-2.569798490321766</v>
+        <v>-2.609033519074403</v>
       </c>
       <c r="P95">
-        <v>-15.03156103243006</v>
+        <v>-15.26105907732562</v>
       </c>
       <c r="Q95">
-        <v>-12.38156103243005</v>
+        <v>-12.61105907732562</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3672908910351093</v>
+        <v>0.4208727062076275</v>
       </c>
       <c r="T95">
-        <v>7.424731894575274</v>
+        <v>8.662187210337821</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.0431758799306164</v>
+        <v>0.04271656205901409</v>
       </c>
       <c r="W95">
-        <v>0.2256191275123607</v>
+        <v>0.2257274346664845</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2957252050042219</v>
+        <v>0.292579192185028</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.237436150958953</v>
+        <v>0.2393361509589531</v>
       </c>
       <c r="C96">
-        <v>-58.18277798387457</v>
+        <v>-59.54164528193114</v>
       </c>
       <c r="D96">
-        <v>28.44575858495762</v>
+        <v>28.2265565695482</v>
       </c>
       <c r="E96">
-        <v>61.16200830411711</v>
+        <v>62.30167358676425</v>
       </c>
       <c r="F96">
-        <v>107.1285365688322</v>
+        <v>108.2682018514793</v>
       </c>
       <c r="G96">
         <v>20.5</v>
@@ -9159,37 +9159,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M96">
-        <v>25.26090892293063</v>
+        <v>25.52964199657883</v>
       </c>
       <c r="N96">
-        <v>-17.87009259640002</v>
+        <v>-18.13882567004822</v>
       </c>
       <c r="O96">
-        <v>-2.609033519074403</v>
+        <v>-2.64826854782704</v>
       </c>
       <c r="P96">
-        <v>-15.26105907732562</v>
+        <v>-15.49055712222118</v>
       </c>
       <c r="Q96">
-        <v>-12.61105907732562</v>
+        <v>-12.84055712222118</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4208727062076275</v>
+        <v>0.4958872474491532</v>
       </c>
       <c r="T96">
-        <v>8.662187210337821</v>
+        <v>10.39462465240539</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04271656205901409</v>
+        <v>0.04226691403734027</v>
       </c>
       <c r="W96">
-        <v>0.2257274346664845</v>
+        <v>0.2258334616699952</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.292579192185028</v>
+        <v>0.2894994112146594</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2393361509589531</v>
+        <v>0.2412361509589531</v>
       </c>
       <c r="C97">
-        <v>-59.54164528193114</v>
+        <v>-60.89716008812635</v>
       </c>
       <c r="D97">
-        <v>28.2265565695482</v>
+        <v>28.01070704600014</v>
       </c>
       <c r="E97">
-        <v>62.30167358676425</v>
+        <v>63.44133886941141</v>
       </c>
       <c r="F97">
-        <v>108.2682018514793</v>
+        <v>109.4078671341265</v>
       </c>
       <c r="G97">
         <v>20.5</v>
@@ -9241,37 +9241,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M97">
-        <v>25.52964199657883</v>
+        <v>25.79837507022703</v>
       </c>
       <c r="N97">
-        <v>-18.13882567004822</v>
+        <v>-18.40755874369642</v>
       </c>
       <c r="O97">
-        <v>-2.64826854782704</v>
+        <v>-2.687503576579676</v>
       </c>
       <c r="P97">
-        <v>-15.49055712222118</v>
+        <v>-15.72005516711674</v>
       </c>
       <c r="Q97">
-        <v>-12.84055712222118</v>
+        <v>-13.07005516711674</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4958872474491532</v>
+        <v>0.6084090593114418</v>
       </c>
       <c r="T97">
-        <v>10.39462465240539</v>
+        <v>12.99328081550675</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.04226691403734027</v>
+        <v>0.04182663368278464</v>
       </c>
       <c r="W97">
-        <v>0.2258334616699952</v>
+        <v>0.2259372797775994</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2894994112146594</v>
+        <v>0.2864837923478399</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2412361509589531</v>
+        <v>0.2431361509589531</v>
       </c>
       <c r="C98">
-        <v>-60.89716008812633</v>
+        <v>-62.24939872867904</v>
       </c>
       <c r="D98">
-        <v>28.01070704600014</v>
+        <v>27.79813368809458</v>
       </c>
       <c r="E98">
-        <v>63.4413388694114</v>
+        <v>64.58100415205854</v>
       </c>
       <c r="F98">
-        <v>109.4078671341265</v>
+        <v>110.5475324167736</v>
       </c>
       <c r="G98">
         <v>20.5</v>
@@ -9323,37 +9323,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M98">
-        <v>25.79837507022702</v>
+        <v>26.06710814387522</v>
       </c>
       <c r="N98">
-        <v>-18.40755874369641</v>
+        <v>-18.67629181734461</v>
       </c>
       <c r="O98">
-        <v>-2.687503576579676</v>
+        <v>-2.726738605332313</v>
       </c>
       <c r="P98">
-        <v>-15.72005516711674</v>
+        <v>-15.9495532120123</v>
       </c>
       <c r="Q98">
-        <v>-13.07005516711674</v>
+        <v>-13.2995532120123</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6084090593114404</v>
+        <v>0.7959454124152537</v>
       </c>
       <c r="T98">
-        <v>12.99328081550671</v>
+        <v>17.32437442067561</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04182663368278464</v>
+        <v>0.04139543127368377</v>
       </c>
       <c r="W98">
-        <v>0.2259372797775994</v>
+        <v>0.2260389573056654</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.28648379234784</v>
+        <v>0.2835303511896149</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2431361509589531</v>
+        <v>0.2450361509589531</v>
       </c>
       <c r="C99">
-        <v>-62.24939872867904</v>
+        <v>-63.59843523029933</v>
       </c>
       <c r="D99">
-        <v>27.79813368809458</v>
+        <v>27.58876246912145</v>
       </c>
       <c r="E99">
-        <v>64.58100415205854</v>
+        <v>65.7206694347057</v>
       </c>
       <c r="F99">
-        <v>110.5475324167736</v>
+        <v>111.6871976994208</v>
       </c>
       <c r="G99">
         <v>20.5</v>
@@ -9405,37 +9405,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M99">
-        <v>26.06710814387522</v>
+        <v>26.33584121752342</v>
       </c>
       <c r="N99">
-        <v>-18.67629181734461</v>
+        <v>-18.94502489099281</v>
       </c>
       <c r="O99">
-        <v>-2.726738605332313</v>
+        <v>-2.76597363408495</v>
       </c>
       <c r="P99">
-        <v>-15.9495532120123</v>
+        <v>-16.17905125690786</v>
       </c>
       <c r="Q99">
-        <v>-13.2995532120123</v>
+        <v>-13.52905125690786</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.7959454124152537</v>
+        <v>1.171018118622881</v>
       </c>
       <c r="T99">
-        <v>17.32437442067561</v>
+        <v>25.98656163101342</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04139543127368377</v>
+        <v>0.04097302891374822</v>
       </c>
       <c r="W99">
-        <v>0.2260389573056654</v>
+        <v>0.2261385597821382</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2835303511896149</v>
+        <v>0.2806371843407413</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2450361509589531</v>
+        <v>0.246936150958953</v>
       </c>
       <c r="C100">
-        <v>-63.59843523029933</v>
+        <v>-64.94434140613873</v>
       </c>
       <c r="D100">
-        <v>27.58876246912145</v>
+        <v>27.38252157592919</v>
       </c>
       <c r="E100">
-        <v>65.7206694347057</v>
+        <v>66.86033471735284</v>
       </c>
       <c r="F100">
-        <v>111.6871976994208</v>
+        <v>112.8268629820679</v>
       </c>
       <c r="G100">
         <v>20.5</v>
@@ -9487,37 +9487,37 @@
         <v>7.390816326530611</v>
       </c>
       <c r="M100">
-        <v>26.33584121752342</v>
+        <v>26.60457429117162</v>
       </c>
       <c r="N100">
-        <v>-18.94502489099281</v>
+        <v>-19.213757964641</v>
       </c>
       <c r="O100">
-        <v>-2.76597363408495</v>
+        <v>-2.805208662837587</v>
       </c>
       <c r="P100">
-        <v>-16.17905125690786</v>
+        <v>-16.40854930180342</v>
       </c>
       <c r="Q100">
-        <v>-13.52905125690786</v>
+        <v>-13.75854930180342</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.171018118622881</v>
+        <v>2.296236237245761</v>
       </c>
       <c r="T100">
-        <v>25.98656163101342</v>
+        <v>51.97312326202683</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04097302891374822</v>
+        <v>0.04055915993482147</v>
       </c>
       <c r="W100">
-        <v>0.2261385597821382</v>
+        <v>0.2262361500873691</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2806371843407413</v>
+        <v>0.2778024653069964</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.246936150958953</v>
-      </c>
-      <c r="C101">
-        <v>-64.94434140613873</v>
-      </c>
-      <c r="D101">
-        <v>27.38252157592919</v>
-      </c>
-      <c r="E101">
-        <v>66.86033471735284</v>
-      </c>
-      <c r="F101">
-        <v>112.8268629820679</v>
-      </c>
-      <c r="G101">
-        <v>20.5</v>
-      </c>
-      <c r="H101">
-        <v>68</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>10.04081632653061</v>
-      </c>
-      <c r="K101">
-        <v>2.65</v>
-      </c>
-      <c r="L101">
-        <v>7.390816326530611</v>
-      </c>
-      <c r="M101">
-        <v>26.60457429117162</v>
-      </c>
-      <c r="N101">
-        <v>-19.213757964641</v>
-      </c>
-      <c r="O101">
-        <v>-2.805208662837587</v>
-      </c>
-      <c r="P101">
-        <v>-16.40854930180342</v>
-      </c>
-      <c r="Q101">
-        <v>-13.75854930180342</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.296236237245761</v>
-      </c>
-      <c r="T101">
-        <v>51.97312326202683</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04055915993482147</v>
-      </c>
-      <c r="W101">
-        <v>0.2262361500873691</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2778024653069964</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
